--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Курс USD/RUB: 88 ₽  |  Обжарочные потери: 20%</t>
+          <t>Скидки: −10% от 10 кг · −20% от 25 кг</t>
         </is>
       </c>
     </row>
@@ -2014,6 +2014,111 @@
       </c>
       <c r="I44" s="15" t="n">
         <v>855</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2847.5</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>585</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Маракуйя</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>5922.5</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>5335</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>4740</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>1138.5</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>1015</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2121,6 +2121,41 @@
         <v>1015</v>
       </c>
     </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Леха Сатори</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>1752.5</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>387</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>345</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2121,41 +2121,6 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Леха Сатори</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>1752.5</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>1580</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>1405</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>430</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>387</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>345</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1473,38 +1473,38 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>625</v>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Вьетнам Блю Шонла</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>2135</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1710</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Адада гр.1 сухой</t>
+          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -1524,22 +1524,22 @@
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>2390</v>
+        <v>3500</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>2155</v>
+        <v>3150</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>1915</v>
+        <v>2800</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>560</v>
+        <v>780</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>504</v>
+        <v>702</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>450</v>
+        <v>625</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
+          <t>Эфиопия Иргач Адада гр.1 сухой</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>2232.5</v>
+        <v>2390</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>2010</v>
+        <v>2155</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1790</v>
+        <v>1915</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>472.5</v>
+        <v>504</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
+          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>2862.5</v>
+        <v>2232.5</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>2580</v>
+        <v>2010</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>2290</v>
+        <v>1790</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>655</v>
+        <v>525</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>589.5</v>
+        <v>472.5</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>525</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
+          <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1650,12 +1650,12 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсило сухой</t>
+          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
+          <t>Колумбия Хайро Арсило сухой</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1699,22 +1699,22 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Смесь Экваториальная</t>
+          <t>Колумбия Гонзало Кормана Катура сухой</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1734,22 +1734,22 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>3020</v>
+        <v>3500</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>2720</v>
+        <v>3150</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2420</v>
+        <v>2800</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>685</v>
+        <v>780</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>616.5</v>
+        <v>702</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>550</v>
+        <v>625</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Арича гр.1 сухой</t>
+          <t>Смесь Экваториальная</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -1788,38 +1788,38 @@
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Арича гр.1 сухой</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>625</v>
+      <c r="D38" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
+          <t>Бразилия SL28 Хани анаэроб.</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+          <t>Бразилия Судан Руме анаэроб.</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1893,34 +1893,38 @@
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr"/>
-      <c r="D41" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>560</v>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -1931,27 +1935,27 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хиросос мытый</t>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr"/>
       <c r="D42" s="15" t="n">
-        <v>2547.5</v>
+        <v>3102.5</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>2295</v>
+        <v>2795</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>2040</v>
+        <v>2485</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>531</v>
+        <v>630</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>475</v>
+        <v>560</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1962,27 +1966,27 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Руанада Нямашеки хилс сухой</t>
+          <t>Колумбия Хиросос мытый</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
       <c r="D43" s="15" t="n">
-        <v>2862.5</v>
+        <v>2547.5</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>2580</v>
+        <v>2295</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2290</v>
+        <v>2040</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>589.5</v>
+        <v>531</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -1993,62 +1997,58 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+          <t>Руанада Нямашеки хилс сухой</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
       <c r="D44" s="15" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="15" t="n">
         <v>4925</v>
       </c>
-      <c r="E44" s="15" t="n">
+      <c r="E45" s="15" t="n">
         <v>4435</v>
       </c>
-      <c r="F44" s="15" t="n">
+      <c r="F45" s="15" t="n">
         <v>3940</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G45" s="15" t="n">
         <v>1065</v>
       </c>
-      <c r="H44" s="15" t="n">
+      <c r="H45" s="15" t="n">
         <v>958.5</v>
       </c>
-      <c r="I44" s="15" t="n">
+      <c r="I45" s="15" t="n">
         <v>855</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Кастильо</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>2847.5</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>2565</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>2280</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>650</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>585</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>520</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Колумбия Пачамама</t>
+          <t>Колумбия Кастильо</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>4842.5</v>
+        <v>2847.5</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>4360</v>
+        <v>2565</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3875</v>
+        <v>2280</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>945</v>
+        <v>585</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>840</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2094,30 +2094,65 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D48" s="12" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E48" s="12" t="n">
         <v>5335</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>4740</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>1015</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1508,38 +1508,38 @@
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>625</v>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Коста-Рика Тарразу мытый</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Адада гр.1 сухой</t>
+          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>2390</v>
+        <v>3500</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>2155</v>
+        <v>3150</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1915</v>
+        <v>2800</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>560</v>
+        <v>780</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>504</v>
+        <v>702</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>450</v>
+        <v>625</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
+          <t>Эфиопия Иргач Адада гр.1 сухой</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>2232.5</v>
+        <v>2390</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>2010</v>
+        <v>2155</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>1790</v>
+        <v>1915</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>472.5</v>
+        <v>504</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
+          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1629,22 +1629,22 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2862.5</v>
+        <v>2232.5</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>2580</v>
+        <v>2010</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>2290</v>
+        <v>1790</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>655</v>
+        <v>525</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>589.5</v>
+        <v>472.5</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>525</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
+          <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1685,12 +1685,12 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсило сухой</t>
+          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
+          <t>Колумбия Хайро Арсило сухой</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1734,22 +1734,22 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Смесь Экваториальная</t>
+          <t>Колумбия Гонзало Кормана Катура сухой</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>3020</v>
+        <v>3500</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>2720</v>
+        <v>3150</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>2420</v>
+        <v>2800</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>685</v>
+        <v>780</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>616.5</v>
+        <v>702</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>550</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Арича гр.1 сухой</t>
+          <t>Смесь Экваториальная</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -1823,38 +1823,38 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Арича гр.1 сухой</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>625</v>
+      <c r="D39" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
+          <t>Бразилия SL28 Хани анаэроб.</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+          <t>Бразилия Судан Руме анаэроб.</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -1928,34 +1928,38 @@
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr"/>
-      <c r="D42" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>560</v>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1966,27 +1970,27 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хиросос мытый</t>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
       <c r="D43" s="15" t="n">
-        <v>2547.5</v>
+        <v>3102.5</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>2295</v>
+        <v>2795</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2040</v>
+        <v>2485</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>531</v>
+        <v>630</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>475</v>
+        <v>560</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -1997,27 +2001,27 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Руанада Нямашеки хилс сухой</t>
+          <t>Колумбия Хиросос мытый</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
       <c r="D44" s="15" t="n">
-        <v>2862.5</v>
+        <v>2547.5</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>2580</v>
+        <v>2295</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2290</v>
+        <v>2040</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>589.5</v>
+        <v>531</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -2028,62 +2032,58 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+          <t>Руанада Нямашеки хилс сухой</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr"/>
       <c r="D45" s="15" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
+      <c r="D46" s="15" t="n">
         <v>4925</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="E46" s="15" t="n">
         <v>4435</v>
       </c>
-      <c r="F45" s="15" t="n">
+      <c r="F46" s="15" t="n">
         <v>3940</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G46" s="15" t="n">
         <v>1065</v>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H46" s="15" t="n">
         <v>958.5</v>
       </c>
-      <c r="I45" s="15" t="n">
+      <c r="I46" s="15" t="n">
         <v>855</v>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Кастильо</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>2847.5</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>2565</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>2280</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>650</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>585</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>520</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Колумбия Пачамама</t>
+          <t>Колумбия Кастильо</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>4842.5</v>
+        <v>2847.5</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>4360</v>
+        <v>2565</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3875</v>
+        <v>2280</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>945</v>
+        <v>585</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>840</v>
+        <v>520</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -2129,30 +2129,65 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>5335</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>4740</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>1015</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1473,73 +1473,73 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Вьетнам Блю Шонла</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>2135</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>1925</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>1710</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>364</v>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>702</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Коста-Рика Тарразу мытый</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>480</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>432</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>384</v>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Иргач Адада гр.1 сухой</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>2390</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>2155</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>1915</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>560</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>504</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
+          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>3500</v>
+        <v>2232.5</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>3150</v>
+        <v>2010</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>2800</v>
+        <v>1790</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>780</v>
+        <v>525</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>702</v>
+        <v>472.5</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>625</v>
+        <v>420</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Адада гр.1 сухой</t>
+          <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>2390</v>
+        <v>2862.5</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>2155</v>
+        <v>2580</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>1915</v>
+        <v>2290</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>560</v>
+        <v>655</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>504</v>
+        <v>589.5</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>450</v>
+        <v>525</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
+          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1629,33 +1629,33 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2232.5</v>
+        <v>2862.5</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>2010</v>
+        <v>2580</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>1790</v>
+        <v>2290</v>
       </c>
       <c r="G33" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I33" s="15" t="n">
         <v>525</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>420</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>микролот • BLACK</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
+          <t>Колумбия Хайро Арсило сухой</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1685,12 +1685,12 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>микролот • BLACK</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
+          <t>Колумбия Гонзало Кормана Катура сухой</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1699,22 +1699,22 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>2862.5</v>
+        <v>3500</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>2580</v>
+        <v>3150</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>2290</v>
+        <v>2800</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>655</v>
+        <v>780</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>589.5</v>
+        <v>702</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>525</v>
+        <v>625</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсило сухой</t>
+          <t>Смесь Экваториальная</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1734,22 +1734,22 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>2862.5</v>
+        <v>3020</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>2580</v>
+        <v>2720</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2290</v>
+        <v>2420</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>589.5</v>
+        <v>616.5</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
+          <t>Эфиопия Арича гр.1 сухой</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -1769,92 +1769,92 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия SL28 Хани анаэроб.</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E38" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F38" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G38" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H38" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I37" s="15" t="n">
+      <c r="I38" s="12" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Смесь Экваториальная</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Судан Руме анаэроб.</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Арича гр.1 сухой</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>550</v>
+      <c r="D39" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
+          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1893,73 +1893,65 @@
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>625</v>
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr"/>
+      <c r="D41" s="15" t="n">
+        <v>3102.5</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>2795</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>2485</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>630</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>625</v>
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Хиросос мытый</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr"/>
+      <c r="D42" s="15" t="n">
+        <v>2547.5</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>2295</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>590</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>531</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>475</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1970,27 +1962,27 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
+          <t>Руанада Нямашеки хилс сухой</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
       <c r="D43" s="15" t="n">
-        <v>3102.5</v>
+        <v>2862.5</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>2795</v>
+        <v>2580</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2485</v>
+        <v>2290</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>700</v>
+        <v>655</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>630</v>
+        <v>589.5</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>560</v>
+        <v>525</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -2001,89 +1993,97 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хиросос мытый</t>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
       <c r="D44" s="15" t="n">
-        <v>2547.5</v>
+        <v>4925</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>2295</v>
+        <v>4435</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2040</v>
+        <v>3940</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>590</v>
+        <v>1065</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>531</v>
+        <v>958.5</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>475</v>
+        <v>855</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>Руанада Нямашеки хилс сухой</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>525</v>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2847.5</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>585</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr"/>
-      <c r="D46" s="15" t="n">
-        <v>4925</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>4435</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>3940</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>1065</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>958.5</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>855</v>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Колумбия Кастильо</t>
+          <t>Колумбия Маракуйя</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -2103,91 +2103,21 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>2847.5</v>
+        <v>5922.5</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>2565</v>
+        <v>5335</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>2280</v>
+        <v>4740</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>650</v>
+        <v>1265</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>585</v>
+        <v>1138.5</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Пачамама</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>4842.5</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>4360</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>3875</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>945</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Маракуйя</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>5922.5</v>
-      </c>
-      <c r="E49" s="12" t="n">
-        <v>5335</v>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>4740</v>
-      </c>
-      <c r="G49" s="12" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>1138.5</v>
-      </c>
-      <c r="I49" s="12" t="n">
         <v>1015</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1473,73 +1473,73 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>625</v>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Вьетнам Блю Шонла</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>2135</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1710</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Иргач Адада гр.1 сухой</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>2390</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>2155</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>1915</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>560</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>504</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>450</v>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Коста-Рика Тарразу мытый</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
+          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>2232.5</v>
+        <v>3500</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>2010</v>
+        <v>3150</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1790</v>
+        <v>2800</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>525</v>
+        <v>780</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>472.5</v>
+        <v>702</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>420</v>
+        <v>625</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
+          <t>Эфиопия Иргач Адада гр.1 сухой</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>2862.5</v>
+        <v>2390</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>2580</v>
+        <v>2155</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>2290</v>
+        <v>1915</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>655</v>
+        <v>560</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>589.5</v>
+        <v>504</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>525</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
+          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1629,33 +1629,33 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2862.5</v>
+        <v>2232.5</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>2580</v>
+        <v>2010</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>2290</v>
+        <v>1790</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>655</v>
+        <v>525</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>589.5</v>
+        <v>472.5</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>525</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсило сухой</t>
+          <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1685,12 +1685,12 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
+          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1699,22 +1699,22 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Смесь Экваториальная</t>
+          <t>Колумбия Хайро Арсило сухой</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1734,22 +1734,22 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>3020</v>
+        <v>2862.5</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>2720</v>
+        <v>2580</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2420</v>
+        <v>2290</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>616.5</v>
+        <v>589.5</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1760,101 +1760,101 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
+          <t>Колумбия Гонзало Кормана Катура сухой</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>702</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Смесь Экваториальная</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
           <t>Эфиопия Арича гр.1 сухой</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D39" s="15" t="n">
         <v>3020</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E39" s="15" t="n">
         <v>2720</v>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F39" s="15" t="n">
         <v>2420</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G39" s="15" t="n">
         <v>685</v>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H39" s="15" t="n">
         <v>616.5</v>
       </c>
-      <c r="I37" s="15" t="n">
+      <c r="I39" s="15" t="n">
         <v>550</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>625</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+          <t>Бразилия SL28 Хани анаэроб.</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1893,65 +1893,73 @@
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr"/>
-      <c r="D41" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>560</v>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Судан Руме анаэроб.</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Хиросос мытый</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr"/>
-      <c r="D42" s="15" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>2295</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>590</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>531</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>475</v>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1962,27 +1970,27 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Руанада Нямашеки хилс сухой</t>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
       <c r="D43" s="15" t="n">
-        <v>2862.5</v>
+        <v>3102.5</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>2580</v>
+        <v>2795</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2290</v>
+        <v>2485</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>589.5</v>
+        <v>630</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -1993,97 +2001,89 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+          <t>Колумбия Хиросос мытый</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
       <c r="D44" s="15" t="n">
+        <v>2547.5</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>2295</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>590</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>531</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Руанада Нямашеки хилс сухой</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="15" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
+      <c r="D46" s="15" t="n">
         <v>4925</v>
       </c>
-      <c r="E44" s="15" t="n">
+      <c r="E46" s="15" t="n">
         <v>4435</v>
       </c>
-      <c r="F44" s="15" t="n">
+      <c r="F46" s="15" t="n">
         <v>3940</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G46" s="15" t="n">
         <v>1065</v>
       </c>
-      <c r="H44" s="15" t="n">
+      <c r="H46" s="15" t="n">
         <v>958.5</v>
       </c>
-      <c r="I44" s="15" t="n">
+      <c r="I46" s="15" t="n">
         <v>855</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Кастильо</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>2847.5</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>2565</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>2280</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>650</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>585</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Пачамама</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>4842.5</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>4360</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>3875</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>945</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>840</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2094,30 +2094,100 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>2847.5</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>585</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>5335</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>4740</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>1015</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1543,38 +1543,38 @@
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>625</v>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Гватемалла Грок</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Адада гр.1 сухой</t>
+          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>2390</v>
+        <v>3500</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>2155</v>
+        <v>3150</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>1915</v>
+        <v>2800</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>560</v>
+        <v>780</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>504</v>
+        <v>702</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>450</v>
+        <v>625</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
+          <t>Эфиопия Иргач Адада гр.1 сухой</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1629,22 +1629,22 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2232.5</v>
+        <v>2390</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>2010</v>
+        <v>2155</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>1790</v>
+        <v>1915</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>472.5</v>
+        <v>504</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
+          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1664,22 +1664,22 @@
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>2862.5</v>
+        <v>2232.5</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>2580</v>
+        <v>2010</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>2290</v>
+        <v>1790</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>655</v>
+        <v>525</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>589.5</v>
+        <v>472.5</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>525</v>
+        <v>420</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
+          <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1720,12 +1720,12 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсило сухой</t>
+          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
+          <t>Колумбия Хайро Арсило сухой</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Смесь Экваториальная</t>
+          <t>Колумбия Гонзало Кормана Катура сухой</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>3020</v>
+        <v>3500</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>2720</v>
+        <v>3150</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>2420</v>
+        <v>2800</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>685</v>
+        <v>780</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>616.5</v>
+        <v>702</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>550</v>
+        <v>625</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Арича гр.1 сухой</t>
+          <t>Смесь Экваториальная</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -1858,38 +1858,38 @@
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Арича гр.1 сухой</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>625</v>
+      <c r="D40" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
+          <t>Бразилия SL28 Хани анаэроб.</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+          <t>Бразилия Судан Руме анаэроб.</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -1963,34 +1963,38 @@
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr"/>
-      <c r="D43" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G43" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>560</v>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -2001,27 +2005,27 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хиросос мытый</t>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
       <c r="D44" s="15" t="n">
-        <v>2547.5</v>
+        <v>3102.5</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>2295</v>
+        <v>2795</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2040</v>
+        <v>2485</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>531</v>
+        <v>630</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>475</v>
+        <v>560</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -2032,27 +2036,27 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Руанада Нямашеки хилс сухой</t>
+          <t>Колумбия Хиросос мытый</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr"/>
       <c r="D45" s="15" t="n">
-        <v>2862.5</v>
+        <v>2547.5</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>2580</v>
+        <v>2295</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>2290</v>
+        <v>2040</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>589.5</v>
+        <v>531</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2063,62 +2067,58 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+          <t>Руанада Нямашеки хилс сухой</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr"/>
       <c r="D46" s="15" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr"/>
+      <c r="D47" s="15" t="n">
         <v>4925</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="E47" s="15" t="n">
         <v>4435</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="F47" s="15" t="n">
         <v>3940</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G47" s="15" t="n">
         <v>1065</v>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H47" s="15" t="n">
         <v>958.5</v>
       </c>
-      <c r="I46" s="15" t="n">
+      <c r="I47" s="15" t="n">
         <v>855</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Кастильо</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>2847.5</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>2565</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>2280</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>650</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>585</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>520</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Колумбия Пачамама</t>
+          <t>Колумбия Кастильо</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -2138,22 +2138,22 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>4842.5</v>
+        <v>2847.5</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>4360</v>
+        <v>2565</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3875</v>
+        <v>2280</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>945</v>
+        <v>585</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>840</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -2164,30 +2164,65 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D50" s="12" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E50" s="12" t="n">
         <v>5335</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>4740</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>1015</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ХАНИ</t>
+          <t>ВЕНЕЦИЯ</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ВЕНЕЦИЯ</t>
+          <t>ХАНИ</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бразилия Серрадо сухой/Бразилия Дарк </t>
+          <t>Бразилия САН РАФАЕЛЬ сухой</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1815</v>
+        <v>1865</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1615</v>
+        <v>1660</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>391.5</v>
+        <v>400.5</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -815,31 +815,31 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Бразилия САН РАФАЕЛЬ сухой</t>
+          <t>Бразилия Серрадо желтый бурбон сухой</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2070</v>
+        <v>2120</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1865</v>
+        <v>1910</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1660</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>400.5</v>
+        <v>409.5</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -850,101 +850,101 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Бразилия Серрадо желтый бурбон сухой</t>
+          <t xml:space="preserve">Бразилия Серрадо сухой/Бразилия Дарк </t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1815</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>435</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Вьетнам Блю Шонла</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>2135</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>1710</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Гватемалла Грок</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>2120</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E13" s="12" t="n">
         <v>1910</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F13" s="12" t="n">
         <v>1700</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G13" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H13" s="12" t="n">
         <v>409.5</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I13" s="12" t="n">
         <v>364</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Гватемалла Декаф</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>2440</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>1955</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>520</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>468</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Гондурас Сан Николас мытый</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>2175</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>1740</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>465</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>372</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -955,31 +955,31 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Кения АА мытый</t>
+          <t>Гватемалла Декаф</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2595</v>
+        <v>2440</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2340</v>
+        <v>2200</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2080</v>
+        <v>1955</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>440</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -990,31 +990,31 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Кения Центральный провинции АБ мытый</t>
+          <t>Гондурас Сан Николас мытый</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2490</v>
+        <v>2175</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2245</v>
+        <v>1960</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1995</v>
+        <v>1740</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>530</v>
+        <v>465</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>477</v>
+        <v>418.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>424</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1025,31 +1025,31 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Колумбия Андино мытый</t>
+          <t>Кения АА мытый</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2175</v>
+        <v>2595</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1960</v>
+        <v>2340</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1740</v>
+        <v>2080</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>465</v>
+        <v>550</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>418.5</v>
+        <v>495</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>372</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1060,66 +1060,66 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Никарагуа Марагаджип мытый</t>
+          <t>Кения Центральный провинции АБ мытый</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2545</v>
+        <v>2490</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2295</v>
+        <v>2245</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2040</v>
+        <v>1995</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Перу Гр.1</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>2230</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>2010</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>1785</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>475</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>427.5</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>380</v>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Китай Симао Гр.1 мытый</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1815</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>435</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>348</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1130,66 +1130,66 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Перу Монте Верде сухой</t>
+          <t>Колумбия Андино мытый</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2620</v>
+        <v>2175</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2360</v>
+        <v>1960</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2100</v>
+        <v>1740</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>555</v>
+        <v>465</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>499.5</v>
+        <v>418.5</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>444</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Руанада Мутителли 15+</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>2230</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>2010</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>1785</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>475</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>427.5</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>380</v>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>🆕 моносорт</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Коста-Рика Тарразу мытый</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1200,31 +1200,31 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Танзания АА</t>
+          <t>Никарагуа Марагаджип мытый</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2335</v>
+        <v>2545</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2105</v>
+        <v>2295</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1870</v>
+        <v>2040</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>495</v>
+        <v>540</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>445.5</v>
+        <v>486</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>396</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Уганда Рувензор сухой</t>
+          <t>Перу Гр.1</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2015</v>
+        <v>2230</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1815</v>
+        <v>2010</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1615</v>
+        <v>1785</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>391.5</v>
+        <v>427.5</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>348</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уганда Вугар Элгон мытый </t>
+          <t>Перу Монте Верде сухой</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2070</v>
+        <v>2620</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1865</v>
+        <v>2360</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1660</v>
+        <v>2100</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>445</v>
+        <v>555</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>400.5</v>
+        <v>499.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>356</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1305,31 +1305,31 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эфиопия Арича Гр.3 сухой </t>
+          <t>Руанада Мутителли 15+</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2175</v>
+        <v>2230</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1960</v>
+        <v>2010</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1740</v>
+        <v>1785</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>418.5</v>
+        <v>427.5</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1340,31 +1340,31 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Гр.4 ТОП сухой /Эфиопи Милк (темн)</t>
+          <t>Танзания АА</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2015</v>
+        <v>2335</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1815</v>
+        <v>2105</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1615</v>
+        <v>1870</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>435</v>
+        <v>495</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>391.5</v>
+        <v>445.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>348</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1375,31 +1375,31 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Эфиопия Лиму Гр.2 мытый</t>
+          <t xml:space="preserve">Уганда Вугар Элгон мытый </t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2120</v>
+        <v>2070</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1910</v>
+        <v>1865</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1700</v>
+        <v>1660</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>409.5</v>
+        <v>400.5</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1410,170 +1410,170 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>Уганда Рувензор сухой</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>1815</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>435</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эфиопия Арича Гр.3 сухой </t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2175</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1740</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Эфиопия Иргач Гр.4 ТОП сухой /Эфиопи Милк (темн)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>1815</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>435</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Эфиопия Лиму Гр.2 мытый</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>455</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
           <t>Эфиопия Сидамо Гр.2 Гуджи мытый</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D31" s="9" t="n">
         <v>2120</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E31" s="9" t="n">
         <v>1910</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F31" s="9" t="n">
         <v>1700</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G31" s="9" t="n">
         <v>455</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H31" s="9" t="n">
         <v>409.5</v>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Китай Симао Гр.1 мытый</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>2015</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>1815</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>1615</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>435</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>391.5</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Вьетнам Блю Шонла</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>2135</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>1925</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>1710</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Коста-Рика Тарразу мытый</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>480</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>432</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Гватемалла Грок</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>2120</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I31" s="12" t="n">
+      <c r="I31" s="9" t="n">
         <v>364</v>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
+          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
+          <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1753,108 +1753,108 @@
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Хайро Арсило сухой</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия SL28 Хани анаэроб.</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>525</v>
+      <c r="D37" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Судан Руме анаэроб.</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E38" s="15" t="n">
+      <c r="E38" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="F38" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H38" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I38" s="15" t="n">
+      <c r="I38" s="12" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Смесь Экваториальная</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>550</v>
+      <c r="D39" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -1865,167 +1865,171 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
+          <t>Колумбия Гонзало Кормана Катура сухой</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>702</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Хайро Арсило сухой</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Смесь Экваториальная</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
           <t>Эфиопия Арича гр.1 сухой</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D43" s="15" t="n">
         <v>3020</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E43" s="15" t="n">
         <v>2720</v>
       </c>
-      <c r="F40" s="15" t="n">
+      <c r="F43" s="15" t="n">
         <v>2420</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G43" s="15" t="n">
         <v>685</v>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H43" s="15" t="n">
         <v>616.5</v>
       </c>
-      <c r="I40" s="15" t="n">
+      <c r="I43" s="15" t="n">
         <v>550</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>702</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr"/>
-      <c r="D44" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>560</v>
+      <c r="D44" s="12" t="n">
+        <v>2847.5</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>585</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -2036,194 +2040,190 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хиросос мытый</t>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr"/>
       <c r="D45" s="15" t="n">
+        <v>3102.5</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>2795</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2485</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>630</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Маракуйя</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>5922.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>5335</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>4740</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>1138.5</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>945</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Хиросос мытый</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr"/>
+      <c r="D48" s="15" t="n">
         <v>2547.5</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="E48" s="15" t="n">
         <v>2295</v>
       </c>
-      <c r="F45" s="15" t="n">
+      <c r="F48" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G48" s="15" t="n">
         <v>590</v>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H48" s="15" t="n">
         <v>531</v>
       </c>
-      <c r="I45" s="15" t="n">
+      <c r="I48" s="15" t="n">
         <v>475</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>микролот</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr"/>
+      <c r="D49" s="15" t="n">
+        <v>4925</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>4435</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>3940</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>958.5</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>Руанада Нямашеки хилс сухой</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr"/>
-      <c r="D46" s="15" t="n">
+      <c r="C50" s="14" t="inlineStr"/>
+      <c r="D50" s="15" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="E50" s="15" t="n">
         <v>2580</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="F50" s="15" t="n">
         <v>2290</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G50" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H50" s="15" t="n">
         <v>589.5</v>
       </c>
-      <c r="I46" s="15" t="n">
+      <c r="I50" s="15" t="n">
         <v>525</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr"/>
-      <c r="D47" s="15" t="n">
-        <v>4925</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>4435</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>3940</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>1065</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>958.5</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Кастильо</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>2847.5</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>2565</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>2280</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>650</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>585</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Пачамама</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>4842.5</v>
-      </c>
-      <c r="E49" s="12" t="n">
-        <v>4360</v>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>3875</v>
-      </c>
-      <c r="G49" s="12" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>945</v>
-      </c>
-      <c r="I49" s="12" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Маракуйя</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>5922.5</v>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>5335</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>4740</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>1138.5</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>1015</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1088,37 +1088,37 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Китай Симао Гр.1 мытый</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>F E</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="9" t="n">
         <v>2015</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="9" t="n">
         <v>1815</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="9" t="n">
         <v>1615</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="9" t="n">
         <v>435</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="9" t="n">
         <v>391.5</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="9" t="n">
         <v>348</v>
       </c>
     </row>
@@ -1753,107 +1753,107 @@
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Бразилия SL28 Хани анаэроб.</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D37" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G37" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="H37" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I37" s="15" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Бразилия Судан Руме анаэроб.</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H38" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I38" s="15" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>🆕 микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H39" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I39" s="15" t="n">
         <v>625</v>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Колумбия Кастильо</t>
+          <t>Кения КиаваМуруру нат.анаэроб.</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -2014,53 +2014,57 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>2847.5</v>
+        <v>3972.5</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>2565</v>
+        <v>3580</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>2280</v>
+        <v>3180</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>650</v>
+        <v>875</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>585</v>
+        <v>787.5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>560</v>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Кения Маакиоу Пиберри</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2960</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>2665</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2370</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>670</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>603</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2071,128 +2075,132 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>2847.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>585</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr"/>
+      <c r="D47" s="15" t="n">
+        <v>3102.5</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>2795</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>2485</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>630</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>🆕 микролот</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D48" s="12" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E48" s="12" t="n">
         <v>5335</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>4740</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>1015</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>🆕 микролот</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Колумбия Пачамама</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>4842.5</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>4360</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>3875</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1050</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>945</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>840</v>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Хиросос мытый</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr"/>
-      <c r="D48" s="15" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>2295</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="G48" s="15" t="n">
-        <v>590</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>531</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr"/>
-      <c r="D49" s="15" t="n">
-        <v>4925</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>4435</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>3940</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>1065</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>958.5</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>855</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -2203,26 +2211,88 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Руанада Нямашеки хилс сухой</t>
+          <t>Колумбия Хиросос мытый</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr"/>
       <c r="D50" s="15" t="n">
+        <v>2547.5</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>2295</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>590</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>531</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr"/>
+      <c r="D51" s="15" t="n">
+        <v>4925</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>4435</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>3940</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>958.5</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Руанада Нямашеки хилс сухой</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr"/>
+      <c r="D52" s="15" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E52" s="15" t="n">
         <v>2580</v>
       </c>
-      <c r="F50" s="15" t="n">
+      <c r="F52" s="15" t="n">
         <v>2290</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G52" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H52" s="15" t="n">
         <v>589.5</v>
       </c>
-      <c r="I50" s="15" t="n">
+      <c r="I52" s="15" t="n">
         <v>525</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,22 +143,22 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,22 +614,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="n">
-        <v>1975</v>
+        <v>1875</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1780</v>
+        <v>1690</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1580</v>
+        <v>1500</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>382.5</v>
+        <v>364.5</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>340</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1910</v>
+        <v>1815</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1720</v>
+        <v>1635</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1530</v>
+        <v>1455</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>369</v>
+        <v>355.5</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -719,22 +719,22 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2070</v>
+        <v>1960</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1865</v>
+        <v>1765</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1660</v>
+        <v>1570</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>400.5</v>
+        <v>378</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>356</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2120</v>
+        <v>2005</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1910</v>
+        <v>1805</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1700</v>
+        <v>1605</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>409.5</v>
+        <v>387</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -859,92 +859,92 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1720</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>410</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>369</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Вьетнам Блю Шонла</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>2015</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E12" s="9" t="n">
         <v>1815</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>1615</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G12" s="9" t="n">
         <v>435</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H12" s="9" t="n">
         <v>391.5</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I12" s="9" t="n">
         <v>348</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Вьетнам Блю Шонла</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Гватемалла Грок</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>F E</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>2135</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>1925</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>1710</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Гватемалла Грок</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>2120</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>364</v>
+      <c r="D13" s="9" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1805</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>387</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2440</v>
+        <v>2295</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2200</v>
+        <v>2070</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1955</v>
+        <v>1840</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>416</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2175</v>
+        <v>2055</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1960</v>
+        <v>1850</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1740</v>
+        <v>1645</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>418.5</v>
+        <v>396</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>372</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1034,22 +1034,22 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2595</v>
+        <v>2440</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2340</v>
+        <v>2200</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2080</v>
+        <v>1955</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>440</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1069,22 +1069,22 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2490</v>
+        <v>2345</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2245</v>
+        <v>2115</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1995</v>
+        <v>1880</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1104,22 +1104,22 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1139,57 +1139,57 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2175</v>
+        <v>2055</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1960</v>
+        <v>1850</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1740</v>
+        <v>1645</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>418.5</v>
+        <v>396</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>372</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>🆕 моносорт</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Коста-Рика Тарразу мытый</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>480</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>432</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>384</v>
+      <c r="D20" s="9" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>455</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1209,22 +1209,22 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2545</v>
+        <v>2390</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2295</v>
+        <v>2155</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2040</v>
+        <v>1915</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>432</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2230</v>
+        <v>2105</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2010</v>
+        <v>1895</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1785</v>
+        <v>1685</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>427.5</v>
+        <v>405</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1279,22 +1279,22 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2620</v>
+        <v>2460</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2360</v>
+        <v>2215</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2100</v>
+        <v>1970</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>555</v>
+        <v>520</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>499.5</v>
+        <v>468</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>444</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2230</v>
+        <v>2105</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2010</v>
+        <v>1895</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1785</v>
+        <v>1685</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>427.5</v>
+        <v>405</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1349,22 +1349,22 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2335</v>
+        <v>2200</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2105</v>
+        <v>1980</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1870</v>
+        <v>1760</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>445.5</v>
+        <v>423</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>396</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1384,22 +1384,22 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2070</v>
+        <v>1960</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1865</v>
+        <v>1765</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1660</v>
+        <v>1570</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>400.5</v>
+        <v>378</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>356</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1454,22 +1454,22 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2175</v>
+        <v>2055</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>1960</v>
+        <v>1850</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1740</v>
+        <v>1645</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>418.5</v>
+        <v>396</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>372</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1489,22 +1489,22 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1524,22 +1524,22 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2120</v>
+        <v>2005</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1910</v>
+        <v>1805</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1700</v>
+        <v>1605</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>409.5</v>
+        <v>387</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1559,518 +1559,518 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2120</v>
+        <v>2005</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1910</v>
+        <v>1805</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1700</v>
+        <v>1605</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>409.5</v>
+        <v>387</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>625</v>
+      <c r="D32" s="12" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>648</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Иргач Адада гр.1 сухой</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D33" s="15" t="n">
-        <v>2390</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>2155</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>1915</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>560</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>504</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>450</v>
+      <c r="D33" s="12" t="n">
+        <v>2187.5</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>520</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>468</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Иргач Билоя гр.2 сухой</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
-        <v>2232.5</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>2010</v>
-      </c>
-      <c r="F34" s="15" t="n">
-        <v>1790</v>
-      </c>
-      <c r="G34" s="15" t="n">
-        <v>525</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>420</v>
+      <c r="D34" s="12" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>1845</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>1640</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>490</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>441</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>395</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Иргач Челелекту мытый гр.1</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G35" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>525</v>
+      <c r="D35" s="12" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>605</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>485</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Челчеле гр.1 сухой</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>525</v>
+      <c r="D36" s="12" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>605</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>485</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Бразилия SL28 Хани анаэроб.</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>625</v>
+      <c r="D37" s="12" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>648</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Бразилия Судан Руме анаэроб.</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>625</v>
+      <c r="D38" s="12" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>648</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>625</v>
+      <c r="D39" s="12" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>648</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Колумбия Гонзало Кормана Катура сухой</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F40" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>625</v>
+      <c r="D40" s="12" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>648</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Колумбия Хайро Арсило сухой</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>525</v>
+      <c r="D41" s="12" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>605</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>485</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Смесь Экваториальная</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>550</v>
+      <c r="D42" s="12" t="n">
+        <v>2765</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>2215</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Арича гр.1 сухой</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G43" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>550</v>
+      <c r="D43" s="12" t="n">
+        <v>2765</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>2215</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>🆕 микролот</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>Кения КиаваМуруру нат.анаэроб.</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>3972.5</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>3580</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>3180</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>875</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>700</v>
+      <c r="D44" s="15" t="n">
+        <v>3627.5</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>3265</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>2905</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>805</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>724.5</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>645</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>🆕 микролот</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Кения Маакиоу Пиберри</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
-        <v>2960</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>2665</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>2370</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>670</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>603</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>540</v>
+      <c r="D45" s="15" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>2435</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2165</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>620</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>558</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>🆕 микролот</t>
+          <t>микролот</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2084,59 +2084,59 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>2847.5</v>
+        <v>2600</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2565</v>
+        <v>2340</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>2280</v>
+        <v>2080</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>585</v>
+        <v>540</v>
       </c>
       <c r="I46" s="12" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>микролот</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr"/>
+      <c r="D47" s="12" t="n">
+        <v>2832.5</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>2270</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>645</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="I47" s="12" t="n">
         <v>520</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr"/>
-      <c r="D47" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>560</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>🆕 микролот</t>
+          <t>микролот</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2150,28 +2150,28 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>5922.5</v>
+        <v>5397.5</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>5335</v>
+        <v>4860</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>4740</v>
+        <v>4320</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1265</v>
+        <v>1160</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1138.5</v>
+        <v>1044</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>1015</v>
+        <v>930</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>🆕 микролот</t>
+          <t>микролот</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2185,115 +2185,115 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>4842.5</v>
+        <v>4415</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>4360</v>
+        <v>3975</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3875</v>
+        <v>3535</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1050</v>
+        <v>965</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>945</v>
+        <v>868.5</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>840</v>
+        <v>775</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>микролот</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Колумбия Хиросос мытый</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr"/>
-      <c r="D50" s="15" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>2295</v>
-      </c>
-      <c r="F50" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>590</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>531</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>475</v>
+      <c r="C50" s="11" t="inlineStr"/>
+      <c r="D50" s="12" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>545</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>микролот</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr"/>
-      <c r="D51" s="15" t="n">
-        <v>4925</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>4435</v>
-      </c>
-      <c r="F51" s="15" t="n">
-        <v>3940</v>
-      </c>
-      <c r="G51" s="15" t="n">
-        <v>1065</v>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>958.5</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>855</v>
+      <c r="C51" s="11" t="inlineStr"/>
+      <c r="D51" s="12" t="n">
+        <v>4490</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>4045</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>3595</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>980</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>882</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>785</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>микролот</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Руанада Нямашеки хилс сухой</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G52" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>525</v>
+      <c r="C52" s="11" t="inlineStr"/>
+      <c r="D52" s="12" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>605</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,22 +143,22 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -550,86 +550,62 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Действует с 01.07.2026 · обновлено 29.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Скидки: −10% от 10 кг · −20% от 25 кг</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Обжарка</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Базовый (1 кг)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>от 10 кг</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>от 25 кг</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Базовый (200 г)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>от 10 кг</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>от 25 кг</t>
         </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>blend Es</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CLASSICA  #1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="6" t="n">
-        <v>1875</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1690</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>405</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>364.5</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>324</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -640,7 +616,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>БИТТЕР</t>
+          <t>CLASSICA #1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -649,22 +625,22 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1815</v>
+        <v>1875</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1635</v>
+        <v>1690</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1455</v>
+        <v>1500</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>355.5</v>
+        <v>364.5</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -675,7 +651,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ВЕНЕЦИЯ</t>
+          <t>БИТТЕР</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -684,22 +660,22 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1910</v>
+        <v>1815</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1720</v>
+        <v>1635</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1530</v>
+        <v>1455</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>369</v>
+        <v>355.5</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -710,7 +686,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ХАНИ</t>
+          <t>ВЕНЕЦИЯ</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -740,17 +716,17 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>blend F</t>
+          <t>blend Es</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ЛУНГО</t>
+          <t>ХАНИ</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -773,38 +749,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Бразилия САН РАФАЕЛЬ сухой</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>1960</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>1765</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>1570</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>420</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>378</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>336</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>blend F</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ЛУНГО</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>BF</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>369</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>328</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -815,31 +791,31 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Бразилия Серрадо желтый бурбон сухой</t>
+          <t>Бразилия Сан Рафаель</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2005</v>
+        <v>1960</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1805</v>
+        <v>1765</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1605</v>
+        <v>1570</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -850,31 +826,31 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бразилия Серрадо сухой/Бразилия Дарк </t>
+          <t>Бразилия Серрадо Желтый бурбон</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1910</v>
+        <v>2005</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1720</v>
+        <v>1805</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1530</v>
+        <v>1605</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -885,31 +861,31 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Вьетнам Блю Шонла</t>
+          <t>Бразилия Серрадо Дарк</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>F E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1615</v>
+        <v>1530</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>391.5</v>
+        <v>369</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -920,7 +896,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Гватемалла Грок</t>
+          <t>Вьетнам Блю Шонла</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -929,22 +905,22 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1605</v>
+        <v>1615</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>387</v>
+        <v>391.5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -955,31 +931,31 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Гватемалла Декаф</t>
+          <t>Гватемала Уэуэтенанго</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F E</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2295</v>
+        <v>2005</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2070</v>
+        <v>1805</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1840</v>
+        <v>1605</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>392</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -990,7 +966,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Гондурас Сан Николас мытый</t>
+          <t>Гватемала Декаф</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -999,22 +975,22 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2055</v>
+        <v>2295</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1850</v>
+        <v>2070</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1645</v>
+        <v>1840</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>396</v>
+        <v>441</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1025,31 +1001,31 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Кения АА мытый</t>
+          <t>Гондурас Сан Николас</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2440</v>
+        <v>2055</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2200</v>
+        <v>1850</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1955</v>
+        <v>1645</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>520</v>
+        <v>440</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>416</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1060,31 +1036,31 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Кения Центральный провинции АБ мытый</t>
+          <t>Кения АА</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2345</v>
+        <v>2440</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2115</v>
+        <v>2200</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1880</v>
+        <v>1955</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1095,31 +1071,31 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Китай Симао Гр.1 мытый</t>
+          <t>Кения АБ Центральная провинция</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>F E</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1910</v>
+        <v>2345</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1720</v>
+        <v>2115</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1530</v>
+        <v>1880</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>369</v>
+        <v>450</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>328</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1130,31 +1106,31 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Колумбия Андино мытый</t>
+          <t>Китай Симао Гр.1</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F E</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2055</v>
+        <v>1910</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1850</v>
+        <v>1720</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1645</v>
+        <v>1530</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>352</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1165,31 +1141,31 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Коста-Рика Тарразу мытый</t>
+          <t>Колумбия Андино</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2120</v>
+        <v>2055</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1910</v>
+        <v>1850</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1700</v>
+        <v>1645</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>409.5</v>
+        <v>396</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1200,7 +1176,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Никарагуа Марагаджип мытый</t>
+          <t>Коста-Рика Тарразу</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1209,22 +1185,22 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2390</v>
+        <v>2120</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2155</v>
+        <v>1910</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1915</v>
+        <v>1700</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>510</v>
+        <v>455</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>459</v>
+        <v>409.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>408</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1235,7 +1211,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Перу Гр.1</t>
+          <t>Никарагуа Марагаджип</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1244,22 +1220,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2105</v>
+        <v>2390</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1895</v>
+        <v>2155</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1685</v>
+        <v>1915</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>405</v>
+        <v>459</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>360</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1270,31 +1246,31 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Перу Монте Верде сухой</t>
+          <t>Перу гр.1</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2460</v>
+        <v>2105</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2215</v>
+        <v>1895</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1970</v>
+        <v>1685</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>468</v>
+        <v>405</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>416</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1305,7 +1281,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Руанада Мутителли 15+</t>
+          <t>Перу Монте Верде</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1314,22 +1290,22 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2105</v>
+        <v>2460</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1895</v>
+        <v>2215</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1685</v>
+        <v>1970</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>360</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1340,7 +1316,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Танзания АА</t>
+          <t>Руанда Мутетели</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1349,22 +1325,22 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2200</v>
+        <v>2105</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1980</v>
+        <v>1895</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1760</v>
+        <v>1685</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1375,31 +1351,31 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уганда Вугар Элгон мытый </t>
+          <t>Танзания АА</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1960</v>
+        <v>2200</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1765</v>
+        <v>1980</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1570</v>
+        <v>1760</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>336</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1410,7 +1386,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Уганда Рувензор сухой</t>
+          <t>Уганда Вугар Элгон</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1419,22 +1395,22 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1910</v>
+        <v>1960</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1720</v>
+        <v>1765</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1530</v>
+        <v>1570</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1445,7 +1421,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эфиопия Арича Гр.3 сухой </t>
+          <t>Уганда Рувензор</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -1454,22 +1430,22 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2055</v>
+        <v>1910</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>1850</v>
+        <v>1720</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1645</v>
+        <v>1530</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>352</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1480,7 +1456,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Эфиопия Иргач Гр.4 ТОП сухой /Эфиопи Милк (темн)</t>
+          <t>Эфиопия Арича гр.3</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1489,22 +1465,22 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>1910</v>
+        <v>2055</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>1720</v>
+        <v>1850</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1530</v>
+        <v>1645</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>328</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1515,31 +1491,31 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Эфиопия Лиму Гр.2 мытый</t>
+          <t>Эфопия Иргачиф Гр.4</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2005</v>
+        <v>1910</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1805</v>
+        <v>1720</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1605</v>
+        <v>1530</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>344</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1550,12 +1526,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Эфиопия Сидамо Гр.2 Гуджи мытый</t>
+          <t>Эфиопия Лиму Гр.2</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
@@ -1578,434 +1554,434 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Клаудиа Колменарес Гейша мытый</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>3192.5</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>2875</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>2555</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>648</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>580</v>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Эфиопия Сидамо Гр.2 Гуджи</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1805</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>387</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>NEW микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Кения Маакиоу Пиберри</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>2435</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>2165</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>620</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>558</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Иргач Адада гр.1 сухой</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D34" s="15" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>2340</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>2080</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Клаудиа Колменарес</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>648</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Лили Роза Варгас Морено</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>2832.5</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>2270</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>645</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Хиросос</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>545</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Руанда Нямашеки Хиллс</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>605</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Ададо</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
         <v>2187.5</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E39" s="15" t="n">
         <v>1970</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F39" s="15" t="n">
         <v>1750</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="G39" s="15" t="n">
         <v>520</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="H39" s="15" t="n">
         <v>468</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="I39" s="15" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Иргач Билоя гр.2 сухой</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Белойя гр.2</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D40" s="15" t="n">
         <v>2045</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E40" s="15" t="n">
         <v>1845</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F40" s="15" t="n">
         <v>1640</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G40" s="15" t="n">
         <v>490</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H40" s="15" t="n">
         <v>441</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I40" s="15" t="n">
         <v>395</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Иргач Челелекту мытый гр.1</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Челелекту гр.1</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D41" s="15" t="n">
         <v>2615</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E41" s="15" t="n">
         <v>2355</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F41" s="15" t="n">
         <v>2095</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G41" s="15" t="n">
         <v>605</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="H41" s="15" t="n">
         <v>544.5</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="I41" s="15" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Челчеле гр.1 сухой</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n">
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Челчеле гр.1</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
         <v>2615</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E42" s="15" t="n">
         <v>2355</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F42" s="15" t="n">
         <v>2095</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G42" s="15" t="n">
         <v>605</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H42" s="15" t="n">
         <v>544.5</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I42" s="15" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия SL28 Хани анаэроб.</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="n">
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Бразилия SL28</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
         <v>3192.5</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E43" s="15" t="n">
         <v>2875</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F43" s="15" t="n">
         <v>2555</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G43" s="15" t="n">
         <v>720</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="H43" s="15" t="n">
         <v>648</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I43" s="15" t="n">
         <v>580</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Судан Руме анаэроб.</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>3192.5</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>2875</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>2555</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>648</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Бразилия Фазенда Лагуинья мундо анаэроб.</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>3192.5</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>2875</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>2555</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>648</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Гонзало Кормана Катура сухой</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>3192.5</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>2875</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>2555</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>648</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Хайро Арсило сухой</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>2615</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>2355</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>2095</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>605</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>544.5</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Смесь Экваториальная</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>2765</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>2490</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>2215</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>571.5</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Арича гр.1 сухой</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>2765</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>2490</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>2215</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>571.5</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>510</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>🆕 микролот</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Кения КиаваМуруру нат.анаэроб.</t>
+          <t>Бразилия Судан Руме</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -2014,68 +1990,68 @@
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>3627.5</v>
+        <v>3192.5</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>3265</v>
+        <v>2875</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2905</v>
+        <v>2555</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>805</v>
+        <v>720</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>724.5</v>
+        <v>648</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>645</v>
+        <v>580</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>🆕 микролот</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Кения Маакиоу Пиберри</t>
+          <t>Бразилия Фазенда Лагуинья мундо</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>2705</v>
+        <v>3192.5</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>2435</v>
+        <v>2875</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>2165</v>
+        <v>2555</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>620</v>
+        <v>720</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>558</v>
+        <v>648</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>микролот</t>
+          <t>NEW микролот • BORЩ</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Колумбия Кастильо</t>
+          <t>Кения КиаваМуруру</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -2084,221 +2060,238 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>2600</v>
+        <v>3627.5</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2340</v>
+        <v>3265</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>2080</v>
+        <v>2905</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>600</v>
+        <v>805</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>540</v>
+        <v>724.5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>480</v>
+        <v>645</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Колумбия Лили Роза Варгас Морено Чирозо Катуа </t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr"/>
-      <c r="D47" s="12" t="n">
-        <v>2832.5</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>2550</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>2270</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>645</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>580.5</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>520</v>
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Гонзало Кармона</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>3192.5</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>2555</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>648</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D48" s="15" t="n">
         <v>5397.5</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="15" t="n">
         <v>4860</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F48" s="15" t="n">
         <v>4320</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="G48" s="15" t="n">
         <v>1160</v>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="H48" s="15" t="n">
         <v>1044</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="I48" s="15" t="n">
         <v>930</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Колумбия Пачамама</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="15" t="n">
         <v>4415</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="15" t="n">
         <v>3975</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="F49" s="15" t="n">
         <v>3535</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="G49" s="15" t="n">
         <v>965</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="H49" s="15" t="n">
         <v>868.5</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="I49" s="15" t="n">
         <v>775</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Хиросос мытый</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr"/>
-      <c r="D50" s="12" t="n">
-        <v>2330</v>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>1865</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>545</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>490.5</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>440</v>
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Хайро Арсила</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>605</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>485</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>КолумбияХайро Асрило инфьюз Маракуйя</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr"/>
-      <c r="D51" s="12" t="n">
-        <v>4490</v>
-      </c>
-      <c r="E51" s="12" t="n">
-        <v>4045</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>3595</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>980</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>882</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>785</v>
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Экваториальный блэнд</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>2765</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>2215</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>635</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>микролот</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Руанада Нямашеки хилс сухой</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr"/>
-      <c r="D52" s="12" t="n">
-        <v>2615</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>2355</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>2095</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>605</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>544.5</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>485</v>
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Арича гр.1</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>2765</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F52" s="15" t="n">
+        <v>2215</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>635</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действует с 01.07.2026 · обновлено 29.06.2026</t>
+          <t>Действует с 01.07.2026 · обновлено 30.06.2026</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1875</v>
+        <v>1975</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1690</v>
+        <v>1780</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1500</v>
+        <v>1580</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>364.5</v>
+        <v>382.5</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1815</v>
+        <v>1910</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1635</v>
+        <v>1720</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1455</v>
+        <v>1530</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>355.5</v>
+        <v>369</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -730,22 +730,22 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -765,22 +765,22 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1960</v>
+        <v>2070</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1765</v>
+        <v>1865</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1570</v>
+        <v>1660</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>378</v>
+        <v>400.5</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>336</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -835,22 +835,22 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2005</v>
+        <v>2120</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1805</v>
+        <v>1910</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1605</v>
+        <v>1700</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>387</v>
+        <v>409.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>344</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -905,22 +905,22 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2015</v>
+        <v>2135</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1815</v>
+        <v>1925</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1615</v>
+        <v>1710</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>391.5</v>
+        <v>409.5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>348</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -940,22 +940,22 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2005</v>
+        <v>2120</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>1805</v>
+        <v>1910</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1605</v>
+        <v>1700</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>387</v>
+        <v>409.5</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>344</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2295</v>
+        <v>2440</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2070</v>
+        <v>2200</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1840</v>
+        <v>1955</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>392</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2055</v>
+        <v>2175</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1850</v>
+        <v>1960</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1645</v>
+        <v>1740</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>396</v>
+        <v>418.5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>352</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1045,22 +1045,22 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2440</v>
+        <v>2595</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2200</v>
+        <v>2340</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1955</v>
+        <v>2080</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2345</v>
+        <v>2490</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2115</v>
+        <v>2245</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1880</v>
+        <v>1995</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>400</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1115,22 +1115,22 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2055</v>
+        <v>2175</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1850</v>
+        <v>1960</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1645</v>
+        <v>1740</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>396</v>
+        <v>418.5</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>352</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2120</v>
+        <v>2250</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1910</v>
+        <v>2025</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>409.5</v>
+        <v>432</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>364</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2390</v>
+        <v>2545</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2155</v>
+        <v>2295</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1915</v>
+        <v>2040</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>408</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2105</v>
+        <v>2230</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1895</v>
+        <v>2010</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1685</v>
+        <v>1785</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>405</v>
+        <v>427.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2460</v>
+        <v>2620</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2215</v>
+        <v>2360</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1970</v>
+        <v>2100</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>520</v>
+        <v>555</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>468</v>
+        <v>499.5</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>416</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1325,22 +1325,22 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2105</v>
+        <v>2230</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1895</v>
+        <v>2010</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1685</v>
+        <v>1785</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>405</v>
+        <v>427.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2200</v>
+        <v>2335</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1980</v>
+        <v>2105</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1760</v>
+        <v>1870</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>423</v>
+        <v>445.5</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>376</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1395,22 +1395,22 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1960</v>
+        <v>2070</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1765</v>
+        <v>1865</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1570</v>
+        <v>1660</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>378</v>
+        <v>400.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>336</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1465,22 +1465,22 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2055</v>
+        <v>2175</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>1850</v>
+        <v>1960</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1645</v>
+        <v>1740</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>396</v>
+        <v>418.5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>352</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1500,22 +1500,22 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1910</v>
+        <v>2015</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1720</v>
+        <v>1815</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1530</v>
+        <v>1615</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>369</v>
+        <v>391.5</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1535,22 +1535,22 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2005</v>
+        <v>2120</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1805</v>
+        <v>1910</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1605</v>
+        <v>1700</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>387</v>
+        <v>409.5</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>344</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1570,22 +1570,22 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2005</v>
+        <v>2120</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>1805</v>
+        <v>1910</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1605</v>
+        <v>1700</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>387</v>
+        <v>409.5</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>344</v>
+        <v>364</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1605,22 +1605,22 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>2705</v>
+        <v>2960</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>2435</v>
+        <v>2665</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>2165</v>
+        <v>2370</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>558</v>
+        <v>603</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1640,22 +1640,22 @@
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>2600</v>
+        <v>2847.5</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>2340</v>
+        <v>2565</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>2080</v>
+        <v>2280</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -1675,22 +1675,22 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>3192.5</v>
+        <v>3500</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>2875</v>
+        <v>3150</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>2555</v>
+        <v>2800</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>648</v>
+        <v>702</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -1710,22 +1710,22 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>2832.5</v>
+        <v>3102.5</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>2550</v>
+        <v>2795</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2270</v>
+        <v>2485</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>580.5</v>
+        <v>630</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1745,22 +1745,22 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>2330</v>
+        <v>2547.5</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>2100</v>
+        <v>2295</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>1865</v>
+        <v>2040</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>545</v>
+        <v>590</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>490.5</v>
+        <v>531</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>2615</v>
+        <v>2862.5</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>2355</v>
+        <v>2580</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>2095</v>
+        <v>2290</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>605</v>
+        <v>655</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>544.5</v>
+        <v>589.5</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>485</v>
+        <v>525</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -1815,22 +1815,22 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>2187.5</v>
+        <v>2390</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>1970</v>
+        <v>2155</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>1750</v>
+        <v>1915</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>2045</v>
+        <v>2232.5</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>1845</v>
+        <v>2010</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1640</v>
+        <v>1790</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>441</v>
+        <v>472.5</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>395</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>2615</v>
+        <v>2862.5</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>2355</v>
+        <v>2580</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>2095</v>
+        <v>2290</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>605</v>
+        <v>655</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>544.5</v>
+        <v>589.5</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>485</v>
+        <v>525</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -1920,22 +1920,22 @@
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>2615</v>
+        <v>2862.5</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>2355</v>
+        <v>2580</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>2095</v>
+        <v>2290</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>605</v>
+        <v>655</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>544.5</v>
+        <v>589.5</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>485</v>
+        <v>525</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1955,22 +1955,22 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>3192.5</v>
+        <v>3500</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>2875</v>
+        <v>3150</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2555</v>
+        <v>2800</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>648</v>
+        <v>702</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -1990,22 +1990,22 @@
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>3192.5</v>
+        <v>3500</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>2875</v>
+        <v>3150</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2555</v>
+        <v>2800</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>648</v>
+        <v>702</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>3192.5</v>
+        <v>3500</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>2875</v>
+        <v>3150</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>2555</v>
+        <v>2800</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>648</v>
+        <v>702</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>3627.5</v>
+        <v>3972.5</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>3265</v>
+        <v>3580</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>2905</v>
+        <v>3180</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>805</v>
+        <v>875</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>724.5</v>
+        <v>787.5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>645</v>
+        <v>700</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2095,22 +2095,22 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>3192.5</v>
+        <v>3500</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>2875</v>
+        <v>3150</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>2555</v>
+        <v>2800</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>648</v>
+        <v>702</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>580</v>
+        <v>625</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -2130,22 +2130,22 @@
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>5397.5</v>
+        <v>5922.5</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>4860</v>
+        <v>5335</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>4320</v>
+        <v>4740</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>1160</v>
+        <v>1265</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>1044</v>
+        <v>1138.5</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>930</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -2165,22 +2165,22 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>4415</v>
+        <v>4842.5</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>3975</v>
+        <v>4360</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>3535</v>
+        <v>3875</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>965</v>
+        <v>1050</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>868.5</v>
+        <v>945</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>775</v>
+        <v>840</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -2200,22 +2200,22 @@
         </is>
       </c>
       <c r="D50" s="15" t="n">
-        <v>2615</v>
+        <v>2862.5</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>2355</v>
+        <v>2580</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>2095</v>
+        <v>2290</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>605</v>
+        <v>655</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>544.5</v>
+        <v>589.5</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>485</v>
+        <v>525</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -2235,22 +2235,22 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>2765</v>
+        <v>3020</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>2490</v>
+        <v>2720</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>2215</v>
+        <v>2420</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>571.5</v>
+        <v>616.5</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -2270,22 +2270,22 @@
         </is>
       </c>
       <c r="D52" s="15" t="n">
-        <v>2765</v>
+        <v>3020</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>2490</v>
+        <v>2720</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>2215</v>
+        <v>2420</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>571.5</v>
+        <v>616.5</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,22 +143,22 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действует с 01.07.2026 · обновлено 30.06.2026</t>
+          <t>Действует с 01.07.2026 · обновлено 07.07.2026</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>NEW микролот • BLACK</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1624,429 +1624,429 @@
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Колумбия Кастильо</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="12" t="n">
         <v>2847.5</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E34" s="12" t="n">
         <v>2565</v>
       </c>
-      <c r="F34" s="15" t="n">
+      <c r="F34" s="12" t="n">
         <v>2280</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="12" t="n">
         <v>650</v>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H34" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="I34" s="15" t="n">
+      <c r="I34" s="12" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Колумбия Клаудиа Колменарес</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E35" s="15" t="n">
+      <c r="E35" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F35" s="15" t="n">
+      <c r="F35" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I35" s="15" t="n">
+      <c r="I35" s="12" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Колумбия Лили Роза Варгас Морено</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="12" t="n">
         <v>3102.5</v>
       </c>
-      <c r="E36" s="15" t="n">
+      <c r="E36" s="12" t="n">
         <v>2795</v>
       </c>
-      <c r="F36" s="15" t="n">
+      <c r="F36" s="12" t="n">
         <v>2485</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="12" t="n">
         <v>700</v>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H36" s="12" t="n">
         <v>630</v>
       </c>
-      <c r="I36" s="15" t="n">
+      <c r="I36" s="12" t="n">
         <v>560</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Колумбия Хиросос</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="12" t="n">
         <v>2547.5</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E37" s="12" t="n">
         <v>2295</v>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F37" s="12" t="n">
         <v>2040</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="12" t="n">
         <v>590</v>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H37" s="12" t="n">
         <v>531</v>
       </c>
-      <c r="I37" s="15" t="n">
+      <c r="I37" s="12" t="n">
         <v>475</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Руанда Нямашеки Хиллс</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="12" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E38" s="15" t="n">
+      <c r="E38" s="12" t="n">
         <v>2580</v>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="F38" s="12" t="n">
         <v>2290</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="12" t="n">
         <v>655</v>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H38" s="12" t="n">
         <v>589.5</v>
       </c>
-      <c r="I38" s="15" t="n">
+      <c r="I38" s="12" t="n">
         <v>525</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Ададо</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
+      <c r="D39" s="12" t="n">
         <v>2390</v>
       </c>
-      <c r="E39" s="15" t="n">
+      <c r="E39" s="12" t="n">
         <v>2155</v>
       </c>
-      <c r="F39" s="15" t="n">
+      <c r="F39" s="12" t="n">
         <v>1915</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="H39" s="15" t="n">
+      <c r="H39" s="12" t="n">
         <v>504</v>
       </c>
-      <c r="I39" s="15" t="n">
+      <c r="I39" s="12" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Белойя гр.2</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="12" t="n">
         <v>2232.5</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E40" s="12" t="n">
         <v>2010</v>
       </c>
-      <c r="F40" s="15" t="n">
+      <c r="F40" s="12" t="n">
         <v>1790</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="12" t="n">
         <v>525</v>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H40" s="12" t="n">
         <v>472.5</v>
       </c>
-      <c r="I40" s="15" t="n">
+      <c r="I40" s="12" t="n">
         <v>420</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Челелекту гр.1</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="12" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="E41" s="12" t="n">
         <v>2580</v>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="F41" s="12" t="n">
         <v>2290</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="12" t="n">
         <v>655</v>
       </c>
-      <c r="H41" s="15" t="n">
+      <c r="H41" s="12" t="n">
         <v>589.5</v>
       </c>
-      <c r="I41" s="15" t="n">
+      <c r="I41" s="12" t="n">
         <v>525</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Челчеле гр.1</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="12" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E42" s="15" t="n">
+      <c r="E42" s="12" t="n">
         <v>2580</v>
       </c>
-      <c r="F42" s="15" t="n">
+      <c r="F42" s="12" t="n">
         <v>2290</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="12" t="n">
         <v>655</v>
       </c>
-      <c r="H42" s="15" t="n">
+      <c r="H42" s="12" t="n">
         <v>589.5</v>
       </c>
-      <c r="I42" s="15" t="n">
+      <c r="I42" s="12" t="n">
         <v>525</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Бразилия SL28</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E43" s="15" t="n">
+      <c r="E43" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F43" s="15" t="n">
+      <c r="F43" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H43" s="15" t="n">
+      <c r="H43" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I43" s="15" t="n">
+      <c r="I43" s="12" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Бразилия Судан Руме</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E44" s="15" t="n">
+      <c r="E44" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F44" s="15" t="n">
+      <c r="F44" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H44" s="15" t="n">
+      <c r="H44" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I44" s="15" t="n">
+      <c r="I44" s="12" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Бразилия Фазенда Лагуинья мундо</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="E45" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F45" s="15" t="n">
+      <c r="F45" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H45" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I45" s="15" t="n">
+      <c r="I45" s="12" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>NEW микролот • BORЩ</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2079,213 +2079,283 @@
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Колумбия Гонзало Кармона</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="E47" s="15" t="n">
+      <c r="E47" s="12" t="n">
         <v>3150</v>
       </c>
-      <c r="F47" s="15" t="n">
+      <c r="F47" s="12" t="n">
         <v>2800</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="12" t="n">
         <v>780</v>
       </c>
-      <c r="H47" s="15" t="n">
+      <c r="H47" s="12" t="n">
         <v>702</v>
       </c>
-      <c r="I47" s="15" t="n">
+      <c r="I47" s="12" t="n">
         <v>625</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="12" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E48" s="15" t="n">
+      <c r="E48" s="12" t="n">
         <v>5335</v>
       </c>
-      <c r="F48" s="15" t="n">
+      <c r="F48" s="12" t="n">
         <v>4740</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H48" s="12" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I48" s="15" t="n">
+      <c r="I48" s="12" t="n">
         <v>1015</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Колумбия Пачамама</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="12" t="n">
         <v>4842.5</v>
       </c>
-      <c r="E49" s="15" t="n">
+      <c r="E49" s="12" t="n">
         <v>4360</v>
       </c>
-      <c r="F49" s="15" t="n">
+      <c r="F49" s="12" t="n">
         <v>3875</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="12" t="n">
         <v>1050</v>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H49" s="12" t="n">
         <v>945</v>
       </c>
-      <c r="I49" s="15" t="n">
+      <c r="I49" s="12" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Колумбия Хайро Арсила</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="12" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E50" s="12" t="n">
         <v>2580</v>
       </c>
-      <c r="F50" s="15" t="n">
+      <c r="F50" s="12" t="n">
         <v>2290</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="12" t="n">
         <v>655</v>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H50" s="12" t="n">
         <v>589.5</v>
       </c>
-      <c r="I50" s="15" t="n">
+      <c r="I50" s="12" t="n">
         <v>525</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Экваториальный блэнд</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="12" t="n">
         <v>3020</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="12" t="n">
         <v>2720</v>
       </c>
-      <c r="F51" s="15" t="n">
+      <c r="F51" s="12" t="n">
         <v>2420</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="12" t="n">
         <v>685</v>
       </c>
-      <c r="H51" s="15" t="n">
+      <c r="H51" s="12" t="n">
         <v>616.5</v>
       </c>
-      <c r="I51" s="15" t="n">
+      <c r="I51" s="12" t="n">
         <v>550</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Эфиопия Арича гр.1</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="12" t="n">
         <v>3020</v>
       </c>
-      <c r="E52" s="15" t="n">
+      <c r="E52" s="12" t="n">
         <v>2720</v>
       </c>
-      <c r="F52" s="15" t="n">
+      <c r="F52" s="12" t="n">
         <v>2420</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="12" t="n">
         <v>685</v>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H52" s="12" t="n">
         <v>616.5</v>
       </c>
-      <c r="I52" s="15" t="n">
+      <c r="I52" s="12" t="n">
         <v>550</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>NEW микролот</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Катимор</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>4602.5</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>4145</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>NEW микролот</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Катуррон</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>4602.5</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>4145</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,22 +143,22 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1554,807 +1554,842 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>NEW моносорт</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Сидамо гр.2</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>2385</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>505</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>454.5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>моносорт</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Эфиопия Сидамо Гр.2 Гуджи</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D33" s="9" t="n">
         <v>2120</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E33" s="9" t="n">
         <v>1910</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F33" s="9" t="n">
         <v>1700</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G33" s="9" t="n">
         <v>455</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H33" s="9" t="n">
         <v>409.5</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I33" s="9" t="n">
         <v>364</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Кения Маакиоу Пиберри</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D34" s="15" t="n">
         <v>2960</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E34" s="15" t="n">
         <v>2665</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F34" s="15" t="n">
         <v>2370</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="G34" s="15" t="n">
         <v>670</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="H34" s="15" t="n">
         <v>603</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="I34" s="15" t="n">
         <v>540</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Колумбия Кастильо</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D35" s="15" t="n">
         <v>2847.5</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E35" s="15" t="n">
         <v>2565</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F35" s="15" t="n">
         <v>2280</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G35" s="15" t="n">
         <v>650</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H35" s="15" t="n">
         <v>585</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I35" s="15" t="n">
         <v>520</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Колумбия Клаудиа Колменарес</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D36" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E36" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F36" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G36" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="H36" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="I36" s="15" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Колумбия Лили Роза Варгас Морено</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D37" s="15" t="n">
         <v>3102.5</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E37" s="15" t="n">
         <v>2795</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F37" s="15" t="n">
         <v>2485</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G37" s="15" t="n">
         <v>700</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H37" s="15" t="n">
         <v>630</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I37" s="15" t="n">
         <v>560</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Колумбия Хиросос</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D38" s="15" t="n">
         <v>2547.5</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E38" s="15" t="n">
         <v>2295</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F38" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G38" s="15" t="n">
         <v>590</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="H38" s="15" t="n">
         <v>531</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I38" s="15" t="n">
         <v>475</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Руанда Нямашеки Хиллс</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D39" s="15" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E39" s="15" t="n">
         <v>2580</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F39" s="15" t="n">
         <v>2290</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G39" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H39" s="15" t="n">
         <v>589.5</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I39" s="15" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Эфиопия Ададо</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D40" s="15" t="n">
         <v>2390</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E40" s="15" t="n">
         <v>2155</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F40" s="15" t="n">
         <v>1915</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G40" s="15" t="n">
         <v>560</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H40" s="15" t="n">
         <v>504</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I40" s="15" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Эфиопия Белойя гр.2</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D41" s="15" t="n">
         <v>2232.5</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E41" s="15" t="n">
         <v>2010</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F41" s="15" t="n">
         <v>1790</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G41" s="15" t="n">
         <v>525</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="H41" s="15" t="n">
         <v>472.5</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I41" s="15" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Эфиопия Челелекту гр.1</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D42" s="15" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E42" s="15" t="n">
         <v>2580</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F42" s="15" t="n">
         <v>2290</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G42" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="H42" s="15" t="n">
         <v>589.5</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I42" s="15" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>микролот • BLACK</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Эфиопия Челчеле гр.1</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D43" s="15" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E43" s="15" t="n">
         <v>2580</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F43" s="15" t="n">
         <v>2290</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G43" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="H43" s="15" t="n">
         <v>589.5</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="I43" s="15" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>Бразилия SL28</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D44" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E44" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F44" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G44" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="H44" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I44" s="15" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Бразилия Судан Руме</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D45" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E45" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F45" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G45" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="H45" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="I45" s="15" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Бразилия Фазенда Лагуинья мундо</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D46" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E46" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F46" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="G46" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="H46" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="I46" s="15" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>Кения КиаваМуруру</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D47" s="15" t="n">
         <v>3972.5</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E47" s="15" t="n">
         <v>3580</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F47" s="15" t="n">
         <v>3180</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G47" s="15" t="n">
         <v>875</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="H47" s="15" t="n">
         <v>787.5</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="I47" s="15" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Колумбия Гонзало Кармона</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D48" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E48" s="15" t="n">
         <v>3150</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F48" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="G48" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="H48" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="I48" s="15" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D49" s="15" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E49" s="15" t="n">
         <v>5335</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F49" s="15" t="n">
         <v>4740</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="G49" s="15" t="n">
         <v>1265</v>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="H49" s="15" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="I49" s="15" t="n">
         <v>1015</v>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>Колумбия Пачамама</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D50" s="15" t="n">
         <v>4842.5</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E50" s="15" t="n">
         <v>4360</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="F50" s="15" t="n">
         <v>3875</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="G50" s="15" t="n">
         <v>1050</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="H50" s="15" t="n">
         <v>945</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="I50" s="15" t="n">
         <v>840</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Колумбия Хайро Арсила</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="D51" s="15" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E51" s="15" t="n">
         <v>2580</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="F51" s="15" t="n">
         <v>2290</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G51" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="H51" s="15" t="n">
         <v>589.5</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="I51" s="15" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>микролот • BORЩ</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Экваториальный блэнд</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D52" s="15" t="n">
         <v>3020</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E52" s="15" t="n">
         <v>2720</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F52" s="15" t="n">
         <v>2420</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="G52" s="15" t="n">
         <v>685</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="H52" s="15" t="n">
         <v>616.5</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Арича гр.1</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>685</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I52" s="12" t="n">
+      <c r="I52" s="15" t="n">
         <v>550</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Арича гр.1</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
           <t>NEW микролот</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Колумбия Катимор</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D54" s="12" t="n">
         <v>4602.5</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="E54" s="12" t="n">
         <v>4145</v>
       </c>
-      <c r="F53" s="15" t="n">
+      <c r="F54" s="12" t="n">
         <v>3685</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G54" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H54" s="12" t="n">
         <v>900</v>
       </c>
-      <c r="I53" s="15" t="n">
+      <c r="I54" s="12" t="n">
         <v>800</v>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>NEW микролот</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Колумбия Катуррон</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D55" s="12" t="n">
         <v>4602.5</v>
       </c>
-      <c r="E54" s="15" t="n">
+      <c r="E55" s="12" t="n">
         <v>4145</v>
       </c>
-      <c r="F54" s="15" t="n">
+      <c r="F55" s="12" t="n">
         <v>3685</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G55" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H55" s="12" t="n">
         <v>900</v>
       </c>
-      <c r="I54" s="15" t="n">
+      <c r="I55" s="12" t="n">
         <v>800</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действует с 01.07.2026 · обновлено 07.07.2026</t>
+          <t>Действует с 01.07.2026 · обновлено 20.08.2026</t>
         </is>
       </c>
     </row>
@@ -1169,38 +1169,38 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Коста-Рика Тарразу</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>480</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>432</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>384</v>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>NEW моносорт</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Риссальда Декаф</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>2245</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>1995</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>477</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>424</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Никарагуа Марагаджип</t>
+          <t>Коста-Рика Тарразу</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2545</v>
+        <v>2250</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2295</v>
+        <v>2025</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2040</v>
+        <v>1800</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>486</v>
+        <v>432</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>432</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Перу гр.1</t>
+          <t>Никарагуа Марагаджип</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2230</v>
+        <v>2545</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2010</v>
+        <v>2295</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1785</v>
+        <v>2040</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>475</v>
+        <v>540</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>427.5</v>
+        <v>486</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>380</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1281,31 +1281,31 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Перу Монте Верде</t>
+          <t>Перу гр.1</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2620</v>
+        <v>2230</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2360</v>
+        <v>2010</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2100</v>
+        <v>1785</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>555</v>
+        <v>475</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>499.5</v>
+        <v>427.5</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>444</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Руанда Мутетели</t>
+          <t>Перу Монте Верде</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1325,22 +1325,22 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2230</v>
+        <v>2620</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2010</v>
+        <v>2360</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1785</v>
+        <v>2100</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>475</v>
+        <v>555</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>427.5</v>
+        <v>499.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>380</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Танзания АА</t>
+          <t>Руанда Мутетели</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2335</v>
+        <v>2230</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2105</v>
+        <v>2010</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1870</v>
+        <v>1785</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>445.5</v>
+        <v>427.5</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1386,31 +1386,31 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Уганда Вугар Элгон</t>
+          <t>Танзания АА</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2070</v>
+        <v>2335</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1865</v>
+        <v>2105</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1660</v>
+        <v>1870</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>400.5</v>
+        <v>445.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>356</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Уганда Рувензор</t>
+          <t>Уганда Вугар Элгон</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>1815</v>
+        <v>1865</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1615</v>
+        <v>1660</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>391.5</v>
+        <v>400.5</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Эфиопия Арича гр.3</t>
+          <t>Уганда Рувензор</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1465,22 +1465,22 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2175</v>
+        <v>2015</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>1960</v>
+        <v>1815</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1740</v>
+        <v>1615</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>418.5</v>
+        <v>391.5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Эфопия Иргачиф Гр.4</t>
+          <t>Эфиопия Арича гр.3</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1500,22 +1500,22 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2015</v>
+        <v>2175</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1815</v>
+        <v>1960</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1615</v>
+        <v>1740</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>391.5</v>
+        <v>418.5</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>348</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1526,66 +1526,66 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
+          <t>Эфопия Иргачиф Гр.4</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1815</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>435</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
           <t>Эфиопия Лиму Гр.2</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D32" s="9" t="n">
         <v>2120</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E32" s="9" t="n">
         <v>1910</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F32" s="9" t="n">
         <v>1700</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G32" s="9" t="n">
         <v>455</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H32" s="9" t="n">
         <v>409.5</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I32" s="9" t="n">
         <v>364</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>NEW моносорт</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Сидамо гр.2</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>2385</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>505</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>454.5</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>404</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1596,66 +1596,66 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
+          <t>Эфиопия Сидамо гр.2</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2385</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>454.5</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>моносорт</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
           <t>Эфиопия Сидамо Гр.2 Гуджи</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>E F</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D34" s="9" t="n">
         <v>2120</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E34" s="9" t="n">
         <v>1910</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F34" s="9" t="n">
         <v>1700</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G34" s="9" t="n">
         <v>455</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H34" s="9" t="n">
         <v>409.5</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I34" s="9" t="n">
         <v>364</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Кения Маакиоу Пиберри</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>2960</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>2665</v>
-      </c>
-      <c r="F34" s="15" t="n">
-        <v>2370</v>
-      </c>
-      <c r="G34" s="15" t="n">
-        <v>670</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>603</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>540</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Кастильо</t>
+          <t>Кения Маакиоу Пиберри</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1675,22 +1675,22 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>2847.5</v>
+        <v>2960</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>2565</v>
+        <v>2665</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>2280</v>
+        <v>2370</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Клаудиа Колменарес</t>
+          <t>Колумбия Кастильо</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1710,22 +1710,22 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>3500</v>
+        <v>2847.5</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>3150</v>
+        <v>2565</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2800</v>
+        <v>2280</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>780</v>
+        <v>650</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>702</v>
+        <v>585</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>625</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Лили Роза Варгас Морено</t>
+          <t>Колумбия Клаудиа Колменарес</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -1745,22 +1745,22 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>3102.5</v>
+        <v>3500</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>2795</v>
+        <v>3150</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>2485</v>
+        <v>2800</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>630</v>
+        <v>702</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>560</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хиросос</t>
+          <t>Колумбия Лили Роза Варгас Морено</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>2547.5</v>
+        <v>3102.5</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>2295</v>
+        <v>2795</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>2040</v>
+        <v>2485</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>531</v>
+        <v>630</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>475</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -1806,31 +1806,31 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Руанда Нямашеки Хиллс</t>
+          <t>Колумбия Хиросос</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>2862.5</v>
+        <v>2547.5</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>2580</v>
+        <v>2295</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>2290</v>
+        <v>2040</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>589.5</v>
+        <v>531</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -1841,66 +1841,66 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Ададо</t>
+          <t>Руанда Нямашеки Хиллс</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>2390</v>
+        <v>2862.5</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>2155</v>
+        <v>2580</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1915</v>
+        <v>2290</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>560</v>
+        <v>655</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>504</v>
+        <v>589.5</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>450</v>
+        <v>525</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Белойя гр.2</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>2232.5</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>2010</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>1790</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>525</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>420</v>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Банко Готити гр. 1</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>2780</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>2505</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2225</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челелекту гр.1</t>
+          <t>Эфиопия Ададо</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -1920,22 +1920,22 @@
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>2862.5</v>
+        <v>2390</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>2580</v>
+        <v>2155</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>2290</v>
+        <v>1915</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>655</v>
+        <v>560</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>589.5</v>
+        <v>504</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>525</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1946,101 +1946,101 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1</t>
+          <t>Эфиопия Белойя гр.2</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>2862.5</v>
+        <v>2232.5</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>2580</v>
+        <v>2010</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>2290</v>
+        <v>1790</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>655</v>
+        <v>525</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>589.5</v>
+        <v>472.5</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>525</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Бразилия SL28</t>
+          <t>Эфиопия Челелекту гр.1</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Бразилия Судан Руме</t>
+          <t>Эфиопия Челчеле гр.1</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Бразилия Фазенда Лагуинья мундо</t>
+          <t>Бразилия SL28</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Кения КиаваМуруру</t>
+          <t>Бразилия Судан Руме</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -2095,22 +2095,22 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>3972.5</v>
+        <v>3500</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>3580</v>
+        <v>3150</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>3180</v>
+        <v>2800</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>875</v>
+        <v>780</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>787.5</v>
+        <v>702</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>700</v>
+        <v>625</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кармона</t>
+          <t>Бразилия Фазенда Лагуинья мундо</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Маракуйя</t>
+          <t>Кения КиаваМуруру</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -2165,22 +2165,22 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>5922.5</v>
+        <v>3972.5</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>5335</v>
+        <v>3580</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>4740</v>
+        <v>3180</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1265</v>
+        <v>875</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>1138.5</v>
+        <v>787.5</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>1015</v>
+        <v>700</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Пачамама</t>
+          <t>Колумбия Гонзало Кармона</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -2200,22 +2200,22 @@
         </is>
       </c>
       <c r="D50" s="15" t="n">
-        <v>4842.5</v>
+        <v>3500</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>4360</v>
+        <v>3150</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>3875</v>
+        <v>2800</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>1050</v>
+        <v>780</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>945</v>
+        <v>702</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>840</v>
+        <v>625</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсила</t>
+          <t>Колумбия Катимор</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -2235,22 +2235,22 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>2862.5</v>
+        <v>4602.5</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>2580</v>
+        <v>4145</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>2290</v>
+        <v>3685</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>655</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>589.5</v>
+        <v>900</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>525</v>
+        <v>800</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Экваториальный блэнд</t>
+          <t>Колумбия Катуррон</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -2270,22 +2270,22 @@
         </is>
       </c>
       <c r="D52" s="15" t="n">
-        <v>3020</v>
+        <v>4602.5</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>2720</v>
+        <v>4145</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>2420</v>
+        <v>3685</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>616.5</v>
+        <v>900</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>550</v>
+        <v>800</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -2296,101 +2296,171 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
+          <t>Колумбия Маракуйя</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>5922.5</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>5335</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>4740</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>1138.5</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Пачамама</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>4360</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>945</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Хайро Арсила</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>655</v>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Экваториальный блэнд</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
           <t>Эфиопия Арича гр.1</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D57" s="15" t="n">
         <v>3020</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="E57" s="15" t="n">
         <v>2720</v>
       </c>
-      <c r="F53" s="15" t="n">
+      <c r="F57" s="15" t="n">
         <v>2420</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G57" s="15" t="n">
         <v>685</v>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H57" s="15" t="n">
         <v>616.5</v>
       </c>
-      <c r="I53" s="15" t="n">
+      <c r="I57" s="15" t="n">
         <v>550</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Катимор</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>4602.5</v>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>4145</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Катуррон</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="n">
-        <v>4602.5</v>
-      </c>
-      <c r="E55" s="12" t="n">
-        <v>4145</v>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G55" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H55" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="I55" s="12" t="n">
-        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2463,6 +2463,41 @@
         <v>550</v>
       </c>
     </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Челчеле гр.1</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>655</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>525</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1</t>
+          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>F E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D58" s="12" t="n">
@@ -2495,6 +2495,41 @@
         <v>589.5</v>
       </c>
       <c r="I58" s="12" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Челчеле гр.1</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>655</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I59" s="12" t="n">
         <v>525</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2009,49 +2009,49 @@
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Челчеле гр.1</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>525</v>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Конга гр.1</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2780</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>2505</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2225</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>микролот • BORЩ</t>
+          <t>микролот • BLACK</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Бразилия SL28</t>
+          <t>Эфиопия Челчеле гр.1</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="D46" s="15" t="n">
-        <v>3500</v>
+        <v>2862.5</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>3150</v>
+        <v>2580</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>2800</v>
+        <v>2290</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>780</v>
+        <v>655</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>702</v>
+        <v>589.5</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>625</v>
+        <v>525</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Бразилия Судан Руме</t>
+          <t>Бразилия SL28</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D47" s="15" t="n">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Бразилия Фазенда Лагуинья мундо</t>
+          <t>Бразилия Судан Руме</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
@@ -2156,31 +2156,31 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Кения КиаваМуруру</t>
+          <t>Бразилия Фазенда Лагуинья мундо</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>3972.5</v>
+        <v>3500</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>3580</v>
+        <v>3150</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>3180</v>
+        <v>2800</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>875</v>
+        <v>780</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>787.5</v>
+        <v>702</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>700</v>
+        <v>625</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Гонзало Кармона</t>
+          <t>Кения КиаваМуруру</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -2200,22 +2200,22 @@
         </is>
       </c>
       <c r="D50" s="15" t="n">
-        <v>3500</v>
+        <v>3972.5</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>3150</v>
+        <v>3580</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>2800</v>
+        <v>3180</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>780</v>
+        <v>875</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>702</v>
+        <v>787.5</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>625</v>
+        <v>700</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катимор</t>
+          <t>Колумбия Гонзало Кармона</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -2235,22 +2235,22 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>4602.5</v>
+        <v>3500</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>4145</v>
+        <v>3150</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>3685</v>
+        <v>2800</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>900</v>
+        <v>702</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>800</v>
+        <v>625</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катуррон</t>
+          <t>Колумбия Катимор</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Маракуйя</t>
+          <t>Колумбия Катуррон</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>5922.5</v>
+        <v>4602.5</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>5335</v>
+        <v>4145</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4740</v>
+        <v>3685</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>1265</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>1138.5</v>
+        <v>900</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>1015</v>
+        <v>800</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Пачамама</t>
+          <t>Колумбия Маракуйя</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -2340,22 +2340,22 @@
         </is>
       </c>
       <c r="D54" s="15" t="n">
-        <v>4842.5</v>
+        <v>5922.5</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>4360</v>
+        <v>5335</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>3875</v>
+        <v>4740</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>1050</v>
+        <v>1265</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>945</v>
+        <v>1138.5</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>840</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Хайро Арсила</t>
+          <t>Колумбия Пачамама</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -2375,22 +2375,22 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>2862.5</v>
+        <v>4842.5</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>2580</v>
+        <v>4360</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2290</v>
+        <v>3875</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>655</v>
+        <v>1050</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>589.5</v>
+        <v>945</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>525</v>
+        <v>840</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>Экваториальный блэнд</t>
+          <t>Колумбия Хайро Арсила</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -2410,22 +2410,22 @@
         </is>
       </c>
       <c r="D56" s="15" t="n">
-        <v>3020</v>
+        <v>2862.5</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>2720</v>
+        <v>2580</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2420</v>
+        <v>2290</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>616.5</v>
+        <v>589.5</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Эфиопия Арича гр.1</t>
+          <t>Экваториальный блэнд</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -2464,38 +2464,38 @@
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Эфиопия Арича гр.1</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D58" s="12" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F58" s="12" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G58" s="12" t="n">
-        <v>655</v>
-      </c>
-      <c r="H58" s="12" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I58" s="12" t="n">
-        <v>525</v>
+      <c r="D58" s="15" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>685</v>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1</t>
+          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>F E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D59" s="12" t="n">
@@ -2530,6 +2530,41 @@
         <v>589.5</v>
       </c>
       <c r="I59" s="12" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Челчеле гр.1</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>655</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I60" s="12" t="n">
         <v>525</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действует с 01.07.2026 · обновлено 20.08.2026</t>
+          <t>Действует с 01.07.2026 · обновлено 21.08.2026</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Гватемала Декаф</t>
+          <t>Гондурас Сан Николас</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2440</v>
+        <v>2175</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2200</v>
+        <v>1960</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1955</v>
+        <v>1740</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>468</v>
+        <v>418.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>416</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1001,31 +1001,31 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Гондурас Сан Николас</t>
+          <t>Кения АА</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2175</v>
+        <v>2595</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1960</v>
+        <v>2340</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1740</v>
+        <v>2080</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>465</v>
+        <v>550</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>418.5</v>
+        <v>495</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>372</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1036,31 +1036,31 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Кения АА</t>
+          <t>Кения АБ Центральная провинция</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2595</v>
+        <v>2490</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2340</v>
+        <v>2245</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2080</v>
+        <v>1995</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>440</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1071,31 +1071,31 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Кения АБ Центральная провинция</t>
+          <t>Китай Симао Гр.1</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>E F</t>
+          <t>F E</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2490</v>
+        <v>2015</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2245</v>
+        <v>1815</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1995</v>
+        <v>1615</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>530</v>
+        <v>435</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>477</v>
+        <v>391.5</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>424</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1106,101 +1106,101 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Китай Симао Гр.1</t>
+          <t>Колумбия Андино</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
+          <t>E F</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>2175</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>1740</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>NEW моносорт</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Колумбия Риссальда Декаф</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
           <t>F E</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>2015</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>1815</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>1615</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>435</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>391.5</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="D20" s="12" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>2245</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>1995</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>477</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>моносорт</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Колумбия Андино</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>2175</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>1740</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>465</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>NEW моносорт</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Колумбия Риссальда Декаф</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>2490</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>2245</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>1995</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>530</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>477</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>424</v>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Коста-Рика Тарразу</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>480</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>432</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Коста-Рика Тарразу</t>
+          <t>Никарагуа Марагаджип</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2250</v>
+        <v>2545</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2025</v>
+        <v>2295</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1800</v>
+        <v>2040</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="H22" s="9" t="n">
+        <v>486</v>
+      </c>
+      <c r="I22" s="9" t="n">
         <v>432</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>384</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Никарагуа Марагаджип</t>
+          <t>Перу гр.1</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2545</v>
+        <v>2230</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2295</v>
+        <v>2010</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2040</v>
+        <v>1785</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>540</v>
+        <v>475</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>486</v>
+        <v>427.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>432</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1281,31 +1281,31 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Перу гр.1</t>
+          <t>Перу Монте Верде</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2230</v>
+        <v>2620</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2010</v>
+        <v>2360</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1785</v>
+        <v>2100</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>475</v>
+        <v>555</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>427.5</v>
+        <v>499.5</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>380</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Перу Монте Верде</t>
+          <t>Руанда Мутетели</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1325,22 +1325,22 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2620</v>
+        <v>2230</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2360</v>
+        <v>2010</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2100</v>
+        <v>1785</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>555</v>
+        <v>475</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>499.5</v>
+        <v>427.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>444</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1351,31 +1351,31 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Руанда Мутетели</t>
+          <t>Уганда Вугар Элгон</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2230</v>
+        <v>2070</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2010</v>
+        <v>1865</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1785</v>
+        <v>1660</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>427.5</v>
+        <v>400.5</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>380</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1386,31 +1386,31 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Танзания АА</t>
+          <t>Уганда Рувензор</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2335</v>
+        <v>2015</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2105</v>
+        <v>1815</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1870</v>
+        <v>1615</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>445.5</v>
+        <v>391.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>396</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1421,31 +1421,31 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Уганда Вугар Элгон</t>
+          <t>Эфиопия Лиму Гр.2</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2070</v>
+        <v>2120</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>1865</v>
+        <v>1910</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1660</v>
+        <v>1700</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>400.5</v>
+        <v>409.5</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1456,217 +1456,217 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Уганда Рувензор</t>
+          <t>Эфиопия Сидамо гр.2</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E F</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2015</v>
+        <v>2385</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>1815</v>
+        <v>2150</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1615</v>
+        <v>1910</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>435</v>
+        <v>505</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>391.5</v>
+        <v>454.5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>348</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Эфиопия Арича гр.3</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>2175</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>1740</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>465</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>372</v>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Кения Маакиоу Пиберри</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>2960</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>2665</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>2370</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>670</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>603</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Эфопия Иргачиф Гр.4</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>2015</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>1815</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>1615</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>435</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>391.5</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>348</v>
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Кастильо</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>2847.5</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>650</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>585</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Эфиопия Лиму Гр.2</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Конга гр.1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>2120</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>1910</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>455</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>364</v>
+      <c r="D32" s="12" t="n">
+        <v>2780</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>2505</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2225</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Эфиопия Сидамо гр.2</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>2385</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>2150</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>1910</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>505</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>454.5</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>404</v>
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Кения КиаваМуруру</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>3972.5</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>3580</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>3180</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>875</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>моносорт</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Эфиопия Сидамо Гр.2 Гуджи</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>2120</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>1910</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>455</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>364</v>
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Колумбия Катимор</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>4602.5</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>4145</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>микролот • BLACK</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Кения Маакиоу Пиберри</t>
+          <t>Колумбия Катуррон</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1675,33 +1675,33 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>2960</v>
+        <v>4602.5</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>2665</v>
+        <v>4145</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>2370</v>
+        <v>3685</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>670</v>
+        <v>1000</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>603</v>
+        <v>900</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>540</v>
+        <v>800</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>микролот • BLACK</t>
+          <t>микролот • BORЩ</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Кастильо</t>
+          <t>Колумбия Маракуйя</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -1710,861 +1710,91 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>2847.5</v>
+        <v>5922.5</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>2565</v>
+        <v>5335</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>2280</v>
+        <v>4740</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>650</v>
+        <v>1265</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>585</v>
+        <v>1138.5</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>520</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Клаудиа Колменарес</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>625</v>
+      <c r="D37" s="12" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>655</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>525</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Лили Роза Варгас Морено</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>3102.5</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>2485</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>630</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Хиросос</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>2295</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>590</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>531</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Руанда Нямашеки Хиллс</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="n">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Челчеле гр.1</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>2862.5</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E38" s="12" t="n">
         <v>2580</v>
       </c>
-      <c r="F40" s="15" t="n">
+      <c r="F38" s="12" t="n">
         <v>2290</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G38" s="12" t="n">
         <v>655</v>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H38" s="12" t="n">
         <v>589.5</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Банко Готити гр. 1</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>2780</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>2505</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>2225</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>571.5</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Ададо</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>2390</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>2155</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>1915</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>560</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>504</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Белойя гр.2</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>2232.5</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>2010</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>1790</v>
-      </c>
-      <c r="G43" s="15" t="n">
-        <v>525</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Челелекту гр.1</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Конга гр.1</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>2780</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>2505</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>2225</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>571.5</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Челчеле гр.1</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Бразилия SL28</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Бразилия Судан Руме</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G48" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Бразилия Фазенда Лагуинья мундо</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>E F</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>Кения КиаваМуруру</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="n">
-        <v>3972.5</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>3580</v>
-      </c>
-      <c r="F50" s="15" t="n">
-        <v>3180</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>875</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Гонзало Кармона</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>3150</v>
-      </c>
-      <c r="F51" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G51" s="15" t="n">
-        <v>780</v>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Катимор</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="n">
-        <v>4602.5</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>4145</v>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G52" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Катуррон</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="n">
-        <v>4602.5</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>4145</v>
-      </c>
-      <c r="F53" s="15" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Маракуйя</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="n">
-        <v>5922.5</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>5335</v>
-      </c>
-      <c r="F54" s="15" t="n">
-        <v>4740</v>
-      </c>
-      <c r="G54" s="15" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>1138.5</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Пачамама</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D55" s="15" t="n">
-        <v>4842.5</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>4360</v>
-      </c>
-      <c r="F55" s="15" t="n">
-        <v>3875</v>
-      </c>
-      <c r="G55" s="15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>945</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Хайро Арсила</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F56" s="15" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G56" s="15" t="n">
-        <v>655</v>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>Экваториальный блэнд</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F57" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G57" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I57" s="15" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>Эфиопия Арича гр.1</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F58" s="15" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G58" s="15" t="n">
-        <v>685</v>
-      </c>
-      <c r="H58" s="15" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I58" s="15" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E59" s="12" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F59" s="12" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G59" s="12" t="n">
-        <v>655</v>
-      </c>
-      <c r="H59" s="12" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Челчеле гр.1</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>F E</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>2862.5</v>
-      </c>
-      <c r="E60" s="12" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>2290</v>
-      </c>
-      <c r="G60" s="12" t="n">
-        <v>655</v>
-      </c>
-      <c r="H60" s="12" t="n">
-        <v>589.5</v>
-      </c>
-      <c r="I60" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>525</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действует с 01.07.2026 · обновлено 21.08.2026</t>
+          <t>Действует с 01.07.2026 · обновлено 24.08.2026</t>
         </is>
       </c>
     </row>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>2490</v>
+        <v>2595</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>2245</v>
+        <v>2340</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>1995</v>
+        <v>2080</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>424</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1554,38 +1554,38 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BLACK</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Конга гр.1</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Кения КиаваМуруру</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
-        <v>2780</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>2505</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>2225</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>571.5</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>510</v>
+      <c r="D32" s="15" t="n">
+        <v>3972.5</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>3580</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>3180</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>875</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Кения КиаваМуруру</t>
+          <t>Колумбия Катимор</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1605,22 +1605,22 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>3972.5</v>
+        <v>4602.5</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>3580</v>
+        <v>4145</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>3180</v>
+        <v>3685</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>787.5</v>
+        <v>900</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катимор</t>
+          <t>Колумбия Катуррон</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катуррон</t>
+          <t>Колумбия Маракуйя</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1675,57 +1675,57 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>4602.5</v>
+        <v>5922.5</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>4145</v>
+        <v>5335</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>3685</v>
+        <v>4740</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>1000</v>
+        <v>1265</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>900</v>
+        <v>1138.5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>800</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Колумбия Маракуйя</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
-        <v>5922.5</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>5335</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>4740</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>1138.5</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>1015</v>
+      <c r="D36" s="12" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>685</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
+          <t>Эфиопия Конга гр.1</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -1745,22 +1745,22 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>2862.5</v>
+        <v>2945</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>2580</v>
+        <v>2655</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2290</v>
+        <v>2360</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>589.5</v>
+        <v>603</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>525</v>
+        <v>540</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>2862.5</v>
+        <v>3020</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>2580</v>
+        <v>2720</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>2290</v>
+        <v>2420</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>589.5</v>
+        <v>616.5</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -1554,38 +1554,38 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Кения КиаваМуруру</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Конга гр.1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
-        <v>3972.5</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>3580</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>3180</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>875</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>700</v>
+      <c r="D32" s="12" t="n">
+        <v>2945</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>2655</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2360</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>670</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>603</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катимор</t>
+          <t>Кения КиаваМуруру</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1605,22 +1605,22 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>4602.5</v>
+        <v>3972.5</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>4145</v>
+        <v>3580</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>3685</v>
+        <v>3180</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>900</v>
+        <v>787.5</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катуррон</t>
+          <t>Колумбия Катимор</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1666,66 +1666,66 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
+          <t>Колумбия Катуррон</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>4602.5</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>4145</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D36" s="15" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E35" s="15" t="n">
+      <c r="E36" s="15" t="n">
         <v>5335</v>
       </c>
-      <c r="F35" s="15" t="n">
+      <c r="F36" s="15" t="n">
         <v>4740</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G36" s="15" t="n">
         <v>1265</v>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H36" s="15" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I35" s="15" t="n">
+      <c r="I36" s="15" t="n">
         <v>1015</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>685</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>550</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Эфиопия Конга гр.1</t>
+          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -1745,22 +1745,22 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>2945</v>
+        <v>3020</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>2655</v>
+        <v>2720</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2360</v>
+        <v>2420</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>603</v>
+        <v>616.5</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1561,66 +1561,62 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
+          <t>Эфиопия Банко Готити гр.1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr"/>
+      <c r="D32" s="12" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>685</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BLACK</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
           <t>Эфиопия Конга гр.1</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D33" s="12" t="n">
         <v>2945</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E33" s="12" t="n">
         <v>2655</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>2360</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>670</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>603</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>540</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Кения КиаваМуруру</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>3972.5</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>3580</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>3180</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>875</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>700</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1631,7 +1627,7 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катимор</t>
+          <t>Кения КиаваМуруру</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1640,22 +1636,22 @@
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>4602.5</v>
+        <v>3972.5</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>4145</v>
+        <v>3580</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>3685</v>
+        <v>3180</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>900</v>
+        <v>787.5</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -1666,7 +1662,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Колумбия Катуррон</t>
+          <t>Колумбия Катимор</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1701,66 +1697,66 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
+          <t>Колумбия Катуррон</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>4602.5</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>4145</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
           <t>Колумбия Маракуйя</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D37" s="15" t="n">
         <v>5922.5</v>
       </c>
-      <c r="E36" s="15" t="n">
+      <c r="E37" s="15" t="n">
         <v>5335</v>
       </c>
-      <c r="F36" s="15" t="n">
+      <c r="F37" s="15" t="n">
         <v>4740</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G37" s="15" t="n">
         <v>1265</v>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H37" s="15" t="n">
         <v>1138.5</v>
       </c>
-      <c r="I36" s="15" t="n">
+      <c r="I37" s="15" t="n">
         <v>1015</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>NEW микролот • BORЩ</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>2420</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>685</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>550</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -1771,12 +1767,12 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Эфиопия Челчеле гр.1</t>
+          <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>F E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
@@ -1795,6 +1791,41 @@
         <v>616.5</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>NEW микролот • BORЩ</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Эфиопия Челчеле гр.1</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>F E</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>685</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="I39" s="12" t="n">
         <v>550</v>
       </c>
     </row>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -19,12 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="53">
   <si>
     <t>ПРАЙС КОФЕ ROASTBERRY</t>
   </si>
   <si>
-    <t>Обновлено 27.08.2026</t>
+    <t>Обновлено 31.08.2026</t>
   </si>
   <si>
     <t>Цены за упаковку · ₽ с НДС</t>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>Эфиопия Банко Готити гр.1</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>Эфиопия Конга гр.1</t>
@@ -414,13 +411,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1299313</xdr:colOff>
+      <xdr:colOff>1312259</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>111081</xdr:rowOff>
+      <xdr:rowOff>229743</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -437,8 +434,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38100" y="47625"/>
-          <a:ext cx="2175613" cy="377781"/>
+          <a:off x="38100" y="9525"/>
+          <a:ext cx="2188559" cy="534543"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1598,7 +1595,7 @@
         <v>44</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D33" s="14">
         <v>3020</v>
@@ -1624,7 +1621,7 @@
         <v>41</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>17</v>
@@ -1650,10 +1647,10 @@
     </row>
     <row r="35" spans="1:9" ht="24" customHeight="1">
       <c r="A35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>17</v>
@@ -1679,10 +1676,10 @@
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1">
       <c r="A36" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>17</v>
@@ -1708,10 +1705,10 @@
     </row>
     <row r="37" spans="1:9" ht="24" customHeight="1">
       <c r="A37" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>17</v>
@@ -1737,10 +1734,10 @@
     </row>
     <row r="38" spans="1:9" ht="24" customHeight="1">
       <c r="A38" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>17</v>
@@ -1766,10 +1763,10 @@
     </row>
     <row r="39" spans="1:9" ht="24" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>17</v>
@@ -1795,10 +1792,10 @@
     </row>
     <row r="40" spans="1:9" ht="24" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>23</v>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Прайс кофе" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс кофе'!$A$5:$I$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Прайс кофе'!$A$1:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс кофе'!$A$5:$I$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Прайс кофе'!$A$1:$I$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Прайс кофе'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="55">
   <si>
     <t>ПРАЙС КОФЕ ROASTBERRY</t>
   </si>
@@ -144,6 +144,9 @@
     <t>Эфиопия Сидамо гр.2</t>
   </si>
   <si>
+    <t>Эфиопия Иргачиф гр.2</t>
+  </si>
+  <si>
     <t>BLACK</t>
   </si>
   <si>
@@ -178,6 +181,9 @@
   </si>
   <si>
     <t>Эфиопия Челчеле гр.1</t>
+  </si>
+  <si>
+    <t>Колумбия Арбуз Декаф</t>
   </si>
 </sst>
 </file>
@@ -735,7 +741,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1511,85 +1517,85 @@
         <v>28</v>
       </c>
       <c r="D30" s="14">
-        <v>2385</v>
+        <v>2230</v>
       </c>
       <c r="E30" s="14">
-        <v>2150</v>
+        <v>2010</v>
       </c>
       <c r="F30" s="14">
-        <v>1910</v>
+        <v>1785</v>
       </c>
       <c r="G30" s="14">
-        <v>505</v>
+        <v>475</v>
       </c>
       <c r="H30" s="15">
-        <v>454.5</v>
+        <v>427.5</v>
       </c>
       <c r="I30" s="14">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="24" customHeight="1">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="14">
+        <v>2335</v>
+      </c>
+      <c r="E31" s="14">
+        <v>2105</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1870</v>
+      </c>
+      <c r="G31" s="14">
+        <v>495</v>
+      </c>
+      <c r="H31" s="15">
+        <v>445.5</v>
+      </c>
+      <c r="I31" s="14">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="24" customHeight="1">
+      <c r="A32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="B32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D32" s="9">
         <v>2960</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E32" s="9">
         <v>2665</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F32" s="9">
         <v>2370</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G32" s="9">
         <v>670</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H32" s="9">
         <v>603</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I32" s="9">
         <v>540</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="24" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="15">
-        <v>2847.5</v>
-      </c>
-      <c r="E32" s="14">
-        <v>2565</v>
-      </c>
-      <c r="F32" s="14">
-        <v>2280</v>
-      </c>
-      <c r="G32" s="14">
-        <v>650</v>
-      </c>
-      <c r="H32" s="14">
-        <v>585</v>
-      </c>
-      <c r="I32" s="14">
-        <v>520</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="24" customHeight="1">
       <c r="A33" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>44</v>
@@ -1597,28 +1603,28 @@
       <c r="C33" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="14">
-        <v>3020</v>
+      <c r="D33" s="15">
+        <v>2847.5</v>
       </c>
       <c r="E33" s="14">
-        <v>2720</v>
+        <v>2565</v>
       </c>
       <c r="F33" s="14">
-        <v>2420</v>
+        <v>2280</v>
       </c>
       <c r="G33" s="14">
-        <v>685</v>
-      </c>
-      <c r="H33" s="15">
-        <v>616.5</v>
+        <v>650</v>
+      </c>
+      <c r="H33" s="14">
+        <v>585</v>
       </c>
       <c r="I33" s="14">
-        <v>550</v>
+        <v>520</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="24" customHeight="1">
       <c r="A34" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>45</v>
@@ -1627,85 +1633,85 @@
         <v>17</v>
       </c>
       <c r="D34" s="14">
+        <v>3020</v>
+      </c>
+      <c r="E34" s="14">
+        <v>2720</v>
+      </c>
+      <c r="F34" s="14">
+        <v>2420</v>
+      </c>
+      <c r="G34" s="14">
+        <v>685</v>
+      </c>
+      <c r="H34" s="15">
+        <v>616.5</v>
+      </c>
+      <c r="I34" s="14">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="24" customHeight="1">
+      <c r="A35" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="14">
         <v>2945</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E35" s="14">
         <v>2655</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F35" s="14">
         <v>2360</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G35" s="14">
         <v>670</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H35" s="14">
         <v>603</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I35" s="14">
         <v>540</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="24" customHeight="1">
-      <c r="A35" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="7" t="s">
+    <row r="36" spans="1:9" ht="24" customHeight="1">
+      <c r="A36" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="B36" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D36" s="10">
         <v>3972.5</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E36" s="9">
         <v>3580</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F36" s="9">
         <v>3180</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G36" s="9">
         <v>875</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H36" s="10">
         <v>787.5</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I36" s="9">
         <v>700</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="24" customHeight="1">
-      <c r="A36" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="15">
-        <v>4602.5</v>
-      </c>
-      <c r="E36" s="14">
-        <v>4145</v>
-      </c>
-      <c r="F36" s="14">
-        <v>3685</v>
-      </c>
-      <c r="G36" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H36" s="14">
-        <v>900</v>
-      </c>
-      <c r="I36" s="14">
-        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="24" customHeight="1">
       <c r="A37" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>49</v>
@@ -1734,7 +1740,7 @@
     </row>
     <row r="38" spans="1:9" ht="24" customHeight="1">
       <c r="A38" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>50</v>
@@ -1743,27 +1749,27 @@
         <v>17</v>
       </c>
       <c r="D38" s="15">
-        <v>5922.5</v>
+        <v>4602.5</v>
       </c>
       <c r="E38" s="14">
-        <v>5335</v>
+        <v>4145</v>
       </c>
       <c r="F38" s="14">
-        <v>4740</v>
+        <v>3685</v>
       </c>
       <c r="G38" s="14">
-        <v>1265</v>
-      </c>
-      <c r="H38" s="15">
-        <v>1138.5</v>
+        <v>1000</v>
+      </c>
+      <c r="H38" s="14">
+        <v>900</v>
       </c>
       <c r="I38" s="14">
-        <v>1015</v>
+        <v>800</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="24" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>51</v>
@@ -1771,34 +1777,34 @@
       <c r="C39" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="14">
-        <v>3020</v>
+      <c r="D39" s="15">
+        <v>5922.5</v>
       </c>
       <c r="E39" s="14">
-        <v>2720</v>
+        <v>5335</v>
       </c>
       <c r="F39" s="14">
-        <v>2420</v>
+        <v>4740</v>
       </c>
       <c r="G39" s="14">
-        <v>685</v>
+        <v>1265</v>
       </c>
       <c r="H39" s="15">
-        <v>616.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I39" s="14">
-        <v>550</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="24" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D40" s="14">
         <v>3020</v>
@@ -1819,8 +1825,66 @@
         <v>550</v>
       </c>
     </row>
+    <row r="41" spans="1:9" ht="24" customHeight="1">
+      <c r="A41" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="14">
+        <v>3020</v>
+      </c>
+      <c r="E41" s="14">
+        <v>2720</v>
+      </c>
+      <c r="F41" s="14">
+        <v>2420</v>
+      </c>
+      <c r="G41" s="14">
+        <v>685</v>
+      </c>
+      <c r="H41" s="15">
+        <v>616.5</v>
+      </c>
+      <c r="I41" s="14">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="24" customHeight="1">
+      <c r="A42" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="14">
+        <v>4130</v>
+      </c>
+      <c r="E42" s="14">
+        <v>3720</v>
+      </c>
+      <c r="F42" s="14">
+        <v>3305</v>
+      </c>
+      <c r="G42" s="14">
+        <v>905</v>
+      </c>
+      <c r="H42" s="15">
+        <v>814.5</v>
+      </c>
+      <c r="I42" s="14">
+        <v>725</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:I40"/>
+  <autoFilter ref="A5:I42"/>
   <mergeCells count="3">
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -114,7 +114,7 @@
     <t>Колумбия Андино</t>
   </si>
   <si>
-    <t>Колумбия Риссальда Декаф</t>
+    <t>Колумбия Рисаральда Декаф</t>
   </si>
   <si>
     <t>Коста-Рика Тарразу</t>
@@ -165,7 +165,7 @@
     <t>BORЩ</t>
   </si>
   <si>
-    <t>Кения КиаваМуруру</t>
+    <t>Кения КиаваМуруру NH-7</t>
   </si>
   <si>
     <t>Колумбия Катимор</t>
@@ -180,7 +180,7 @@
     <t>Эфиопия Гедеб гр.1 Ананасовый настой</t>
   </si>
   <si>
-    <t>Эфиопия Челчеле гр.1</t>
+    <t>Эфиопия ВОРКА Челчеле гр.1 анаэроб.</t>
   </si>
   <si>
     <t>Колумбия Арбуз Декаф</t>
@@ -1427,7 +1427,7 @@
         <v>37</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D27" s="14">
         <v>2070</v>
@@ -1862,7 +1862,7 @@
         <v>54</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D42" s="14">
         <v>4130</v>

--- a/tma_static/data/Roastberry_Прайс_2026.xlsx
+++ b/tma_static/data/Roastberry_Прайс_2026.xlsx
@@ -51,13 +51,13 @@
     <t>базовая 200 г</t>
   </si>
   <si>
-    <t>СМЕСИ</t>
+    <t>смеси</t>
   </si>
   <si>
     <t>CLASSICA #1</t>
   </si>
   <si>
-    <t>Эспрессо</t>
+    <t>эспрессо</t>
   </si>
   <si>
     <t>БИТТЕР</t>
@@ -72,10 +72,10 @@
     <t>ЛУНГО</t>
   </si>
   <si>
-    <t>Фильтр</t>
-  </si>
-  <si>
-    <t>МОНОСОРТА</t>
+    <t>фильтр</t>
+  </si>
+  <si>
+    <t>моносорта</t>
   </si>
   <si>
     <t>Бразилия Сан Рафаель</t>
@@ -90,7 +90,7 @@
     <t>Вьетнам Блю Шонла</t>
   </si>
   <si>
-    <t>Фильтр, Эспрессо</t>
+    <t>фильтр, эспрессо</t>
   </si>
   <si>
     <t>Гватемала Уэуэтенанго</t>
@@ -105,7 +105,7 @@
     <t>Кения АБ Центральная провинция</t>
   </si>
   <si>
-    <t>Эспрессо, Фильтр</t>
+    <t>эспрессо, фильтр</t>
   </si>
   <si>
     <t>Китай Симао Гр.1</t>
@@ -147,7 +147,7 @@
     <t>Эфиопия Иргачиф гр.2</t>
   </si>
   <si>
-    <t>BLACK</t>
+    <t>блэк</t>
   </si>
   <si>
     <t>Кения Маакиоу Пиберри</t>
@@ -162,7 +162,7 @@
     <t>Эфиопия Конга гр.1</t>
   </si>
   <si>
-    <t>BORЩ</t>
+    <t>борщ</t>
   </si>
   <si>
     <t>Кения КиаваМуруру NH-7</t>
